--- a/data/excel/TestData.xlsx
+++ b/data/excel/TestData.xlsx
@@ -1,49 +1,115 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <workbookPr codeName="ThisWorkbook"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
+  <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
   <sheets>
-    <sheet name="Login" sheetId="1" r:id="rId1"/>
-    <sheet name="Dashboard" sheetId="2" r:id="rId2"/>
-    <sheet name="ForgotPassword" sheetId="3" r:id="rId3"/>
+    <sheet sheetId="1" name="Login" state="visible" r:id="rId4"/>
+    <sheet sheetId="2" name="Dashboard" state="visible" r:id="rId5"/>
+    <sheet sheetId="3" name="ForgotPassword" state="visible" r:id="rId6"/>
   </sheets>
+  <calcPr calcId="171027"/>
 </workbook>
 </file>
 
-<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
-  <metadataTypes count="1">
-    <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
-  </metadataTypes>
-  <futureMetadata name="XLDAPR" count="1">
-    <bk>
-      <extLst>
-        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
-          <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
-        </ext>
-      </extLst>
-    </bk>
-  </futureMetadata>
-  <cellMetadata count="1">
-    <bk>
-      <rc t="1" v="0"/>
-    </bk>
-  </cellMetadata>
-</metadata>
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="28">
+  <si>
+    <t>Key</t>
+  </si>
+  <si>
+    <t>Value</t>
+  </si>
+  <si>
+    <t>title</t>
+  </si>
+  <si>
+    <t>EMIS | Tamil Nadu Schools</t>
+  </si>
+  <si>
+    <t>validUser</t>
+  </si>
+  <si>
+    <t>validPassword</t>
+  </si>
+  <si>
+    <t>Test@123</t>
+  </si>
+  <si>
+    <t>invalidUser</t>
+  </si>
+  <si>
+    <t>jkdbfbjdsbvi</t>
+  </si>
+  <si>
+    <t>invalidPassword</t>
+  </si>
+  <si>
+    <t>dhhdsuivb</t>
+  </si>
+  <si>
+    <t>space</t>
+  </si>
+  <si>
+    <t xml:space="preserve">   </t>
+  </si>
+  <si>
+    <t>username</t>
+  </si>
+  <si>
+    <t>password</t>
+  </si>
+  <si>
+    <t>test@123</t>
+  </si>
+  <si>
+    <t>invalidUser1</t>
+  </si>
+  <si>
+    <t>40286@..09</t>
+  </si>
+  <si>
+    <t>invalidUser2</t>
+  </si>
+  <si>
+    <t>spaceUser</t>
+  </si>
+  <si>
+    <t>invalidOtp1</t>
+  </si>
+  <si>
+    <t>invalidOtp2</t>
+  </si>
+  <si>
+    <t>@@@@.....</t>
+  </si>
+  <si>
+    <t>validOtp</t>
+  </si>
+  <si>
+    <t>invalidPassword1</t>
+  </si>
+  <si>
+    <t>invalidPassword2</t>
+  </si>
+  <si>
+    <t>test123</t>
+  </si>
+  <si>
+    <t>Test@1234</t>
+  </si>
+</sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:vt="http://schemas.openxmlformats.org/officeDocument/2006/docPropsVTypes">
-  <numFmts count="1">
-    <numFmt numFmtId="56" formatCode="&quot;上午/下午 &quot;hh&quot;時&quot;mm&quot;分&quot;ss&quot;秒 &quot;"/>
-  </numFmts>
-  <fonts count="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+  <fonts count="1" x14ac:knownFonts="1">
     <font>
-      <sz val="12"/>
       <color theme="1"/>
-      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+      <sz val="11"/>
+      <name val="Calibri"/>
     </font>
   </fonts>
   <fills count="2">
@@ -67,13 +133,21 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleMedium4"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -398,202 +472,202 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:B7"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <cols>
+    <col min="1" max="24" width="13.571428571428571" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="str">
-        <v>Key</v>
-      </c>
-      <c r="B1" t="str">
-        <v>Value</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="str">
-        <v>title</v>
-      </c>
-      <c r="B2" t="str">
-        <v>EMIS | Tamil Nadu Schools</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="str">
-        <v>validUser</v>
-      </c>
-      <c r="B3" t="str">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>2</v>
+      </c>
+      <c r="B2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>4</v>
+      </c>
+      <c r="B3">
         <v>4028609</v>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" t="str">
-        <v>validPassword</v>
-      </c>
-      <c r="B4" t="str">
-        <v>Test@123</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="str">
-        <v>invalidUser</v>
-      </c>
-      <c r="B5" t="str">
-        <v>jkdbfbjdsbvi</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="str">
-        <v>invalidPassword</v>
-      </c>
-      <c r="B6" t="str">
-        <v>dhhdsuivb</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="str">
-        <v>space</v>
-      </c>
-      <c r="B7" t="str">
-        <v xml:space="preserve">   </v>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>5</v>
+      </c>
+      <c r="B4" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>7</v>
+      </c>
+      <c r="B5" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B6" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>11</v>
+      </c>
+      <c r="B7" t="s">
+        <v>12</v>
       </c>
     </row>
   </sheetData>
-  <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:B7"/>
-  </ignoredErrors>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:B3"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <cols>
+    <col min="1" max="24" width="13.571428571428571" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="str">
-        <v>Key</v>
-      </c>
-      <c r="B1" t="str">
-        <v>Value</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="str">
-        <v>username</v>
-      </c>
-      <c r="B2" t="str">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>13</v>
+      </c>
+      <c r="B2">
         <v>4028609</v>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" t="str">
-        <v>password</v>
-      </c>
-      <c r="B3" t="str">
-        <v>Test@123</v>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>14</v>
+      </c>
+      <c r="B3" t="s">
+        <v>15</v>
       </c>
     </row>
   </sheetData>
-  <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:B3"/>
-  </ignoredErrors>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:B11"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <cols>
+    <col min="1" max="24" width="13.571428571428571" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="str">
-        <v>Key</v>
-      </c>
-      <c r="B1" t="str">
-        <v>Value</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="str">
-        <v>validUser</v>
-      </c>
-      <c r="B2" t="str">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B2">
         <v>4028609</v>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" t="str">
-        <v>invalidUser1</v>
-      </c>
-      <c r="B3" t="str">
-        <v>40286@..09</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="str">
-        <v>invalidUser2</v>
-      </c>
-      <c r="B4" t="str">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>16</v>
+      </c>
+      <c r="B3" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>18</v>
+      </c>
+      <c r="B4">
         <v>4028609548494</v>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" t="str">
-        <v>spaceUser</v>
-      </c>
-      <c r="B5" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="str">
-        <v>invalidOtp1</v>
-      </c>
-      <c r="B6" t="str">
+    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>20</v>
+      </c>
+      <c r="B6">
         <v>8555555</v>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" t="str">
-        <v>invalidOtp2</v>
-      </c>
-      <c r="B7" t="str">
-        <v>@@@@.....</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="str">
-        <v>validOtp</v>
-      </c>
-      <c r="B8" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="str">
-        <v>invalidPassword1</v>
-      </c>
-      <c r="B9" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="str">
-        <v>invalidPassword2</v>
-      </c>
-      <c r="B10" t="str">
-        <v>test123</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="str">
-        <v>validPassword</v>
-      </c>
-      <c r="B11" t="str">
-        <v>Test@1234</v>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>21</v>
+      </c>
+      <c r="B7" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="8" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="9" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>25</v>
+      </c>
+      <c r="B10" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>5</v>
+      </c>
+      <c r="B11" t="s">
+        <v>27</v>
       </c>
     </row>
   </sheetData>
-  <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:B11"/>
-  </ignoredErrors>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>
 </file>
--- a/data/excel/TestData.xlsx
+++ b/data/excel/TestData.xlsx
@@ -13,12 +13,15 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="47" uniqueCount="29">
   <si>
     <t>Key</t>
   </si>
   <si>
-    <t>Value</t>
+    <t>staging</t>
+  </si>
+  <si>
+    <t>production</t>
   </si>
   <si>
     <t>title</t>
@@ -33,7 +36,10 @@
     <t>validPassword</t>
   </si>
   <si>
-    <t>Test@123</t>
+    <t>test@123</t>
+  </si>
+  <si>
+    <t>Pete@9119</t>
   </si>
   <si>
     <t>invalidUser</t>
@@ -58,9 +64,6 @@
   </si>
   <si>
     <t>password</t>
-  </si>
-  <si>
-    <t>test@123</t>
   </si>
   <si>
     <t>invalidUser1</t>
@@ -103,7 +106,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <color theme="1"/>
       <family val="2"/>
@@ -111,16 +114,32 @@
       <sz val="11"/>
       <name val="Calibri"/>
     </font>
+    <font>
+      <b/>
+      <i/>
+      <sz val="16"/>
+      <name val="Times New Roman"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF538136"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE3EFD9"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -128,12 +147,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -473,67 +501,1093 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:B7"/>
+  <dimension ref="A1:X40"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
-    <col min="1" max="24" width="13.571428571428571" customWidth="1"/>
+    <col min="1" max="24" width="20.571428571428573" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A1" t="s">
+    <row r="1" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="B2" t="s">
+      <c r="D1" s="1"/>
+      <c r="E1" s="1"/>
+      <c r="F1" s="1"/>
+      <c r="G1" s="1"/>
+      <c r="H1" s="1"/>
+      <c r="I1" s="1"/>
+      <c r="J1" s="1"/>
+      <c r="K1" s="1"/>
+      <c r="L1" s="1"/>
+      <c r="M1" s="1"/>
+      <c r="N1" s="1"/>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+      <c r="T1" s="1"/>
+      <c r="U1" s="1"/>
+      <c r="V1" s="1"/>
+      <c r="W1" s="1"/>
+      <c r="X1" s="1"/>
+    </row>
+    <row r="2" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A2" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
+      <c r="B2" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="B3">
+      <c r="C2" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="D2" s="2"/>
+      <c r="E2" s="2"/>
+      <c r="F2" s="2"/>
+      <c r="G2" s="2"/>
+      <c r="H2" s="2"/>
+      <c r="I2" s="2"/>
+      <c r="J2" s="2"/>
+      <c r="K2" s="2"/>
+      <c r="L2" s="2"/>
+      <c r="M2" s="2"/>
+      <c r="N2" s="2"/>
+      <c r="O2" s="2"/>
+      <c r="P2" s="2"/>
+      <c r="Q2" s="2"/>
+      <c r="R2" s="2"/>
+      <c r="S2" s="2"/>
+      <c r="T2" s="2"/>
+      <c r="U2" s="2"/>
+      <c r="V2" s="2"/>
+      <c r="W2" s="2"/>
+      <c r="X2" s="2"/>
+    </row>
+    <row r="3" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A3" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B3" s="2">
         <v>4028609</v>
       </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>5</v>
-      </c>
-      <c r="B4" t="s">
+      <c r="C3" s="2">
+        <v>4028619</v>
+      </c>
+      <c r="D3" s="2"/>
+      <c r="E3" s="2"/>
+      <c r="F3" s="2"/>
+      <c r="G3" s="2"/>
+      <c r="H3" s="2"/>
+      <c r="I3" s="2"/>
+      <c r="J3" s="2"/>
+      <c r="K3" s="2"/>
+      <c r="L3" s="2"/>
+      <c r="M3" s="2"/>
+      <c r="N3" s="2"/>
+      <c r="O3" s="2"/>
+      <c r="P3" s="2"/>
+      <c r="Q3" s="2"/>
+      <c r="R3" s="2"/>
+      <c r="S3" s="2"/>
+      <c r="T3" s="2"/>
+      <c r="U3" s="2"/>
+      <c r="V3" s="2"/>
+      <c r="W3" s="2"/>
+      <c r="X3" s="2"/>
+    </row>
+    <row r="4" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A4" s="2" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
+      <c r="B4" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="B5" t="s">
+      <c r="C4" s="2" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
+      <c r="D4" s="2"/>
+      <c r="E4" s="2"/>
+      <c r="F4" s="2"/>
+      <c r="G4" s="2"/>
+      <c r="H4" s="2"/>
+      <c r="I4" s="2"/>
+      <c r="J4" s="2"/>
+      <c r="K4" s="2"/>
+      <c r="L4" s="2"/>
+      <c r="M4" s="2"/>
+      <c r="N4" s="2"/>
+      <c r="O4" s="2"/>
+      <c r="P4" s="2"/>
+      <c r="Q4" s="2"/>
+      <c r="R4" s="2"/>
+      <c r="S4" s="2"/>
+      <c r="T4" s="2"/>
+      <c r="U4" s="2"/>
+      <c r="V4" s="2"/>
+      <c r="W4" s="2"/>
+      <c r="X4" s="2"/>
+    </row>
+    <row r="5" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A5" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="B6" t="s">
+      <c r="B5" s="2" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
+      <c r="C5" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D5" s="2"/>
+      <c r="E5" s="2"/>
+      <c r="F5" s="2"/>
+      <c r="G5" s="2"/>
+      <c r="H5" s="2"/>
+      <c r="I5" s="2"/>
+      <c r="J5" s="2"/>
+      <c r="K5" s="2"/>
+      <c r="L5" s="2"/>
+      <c r="M5" s="2"/>
+      <c r="N5" s="2"/>
+      <c r="O5" s="2"/>
+      <c r="P5" s="2"/>
+      <c r="Q5" s="2"/>
+      <c r="R5" s="2"/>
+      <c r="S5" s="2"/>
+      <c r="T5" s="2"/>
+      <c r="U5" s="2"/>
+      <c r="V5" s="2"/>
+      <c r="W5" s="2"/>
+      <c r="X5" s="2"/>
+    </row>
+    <row r="6" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A6" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="B7" t="s">
+      <c r="B6" s="2" t="s">
         <v>12</v>
       </c>
+      <c r="C6" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D6" s="2"/>
+      <c r="E6" s="2"/>
+      <c r="F6" s="2"/>
+      <c r="G6" s="2"/>
+      <c r="H6" s="2"/>
+      <c r="I6" s="2"/>
+      <c r="J6" s="2"/>
+      <c r="K6" s="2"/>
+      <c r="L6" s="2"/>
+      <c r="M6" s="2"/>
+      <c r="N6" s="2"/>
+      <c r="O6" s="2"/>
+      <c r="P6" s="2"/>
+      <c r="Q6" s="2"/>
+      <c r="R6" s="2"/>
+      <c r="S6" s="2"/>
+      <c r="T6" s="2"/>
+      <c r="U6" s="2"/>
+      <c r="V6" s="2"/>
+      <c r="W6" s="2"/>
+      <c r="X6" s="2"/>
+    </row>
+    <row r="7" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A7" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D7" s="2"/>
+      <c r="E7" s="2"/>
+      <c r="F7" s="2"/>
+      <c r="G7" s="2"/>
+      <c r="H7" s="2"/>
+      <c r="I7" s="2"/>
+      <c r="J7" s="2"/>
+      <c r="K7" s="2"/>
+      <c r="L7" s="2"/>
+      <c r="M7" s="2"/>
+      <c r="N7" s="2"/>
+      <c r="O7" s="2"/>
+      <c r="P7" s="2"/>
+      <c r="Q7" s="2"/>
+      <c r="R7" s="2"/>
+      <c r="S7" s="2"/>
+      <c r="T7" s="2"/>
+      <c r="U7" s="2"/>
+      <c r="V7" s="2"/>
+      <c r="W7" s="2"/>
+      <c r="X7" s="2"/>
+    </row>
+    <row r="8" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A8" s="2"/>
+      <c r="B8" s="2"/>
+      <c r="C8" s="2"/>
+      <c r="D8" s="2"/>
+      <c r="E8" s="2"/>
+      <c r="F8" s="2"/>
+      <c r="G8" s="2"/>
+      <c r="H8" s="2"/>
+      <c r="I8" s="2"/>
+      <c r="J8" s="2"/>
+      <c r="K8" s="2"/>
+      <c r="L8" s="2"/>
+      <c r="M8" s="2"/>
+      <c r="N8" s="2"/>
+      <c r="O8" s="2"/>
+      <c r="P8" s="2"/>
+      <c r="Q8" s="2"/>
+      <c r="R8" s="2"/>
+      <c r="S8" s="2"/>
+      <c r="T8" s="2"/>
+      <c r="U8" s="2"/>
+      <c r="V8" s="2"/>
+      <c r="W8" s="2"/>
+      <c r="X8" s="2"/>
+    </row>
+    <row r="9" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A9" s="2"/>
+      <c r="B9" s="2"/>
+      <c r="C9" s="2"/>
+      <c r="D9" s="2"/>
+      <c r="E9" s="2"/>
+      <c r="F9" s="2"/>
+      <c r="G9" s="2"/>
+      <c r="H9" s="2"/>
+      <c r="I9" s="2"/>
+      <c r="J9" s="2"/>
+      <c r="K9" s="2"/>
+      <c r="L9" s="2"/>
+      <c r="M9" s="2"/>
+      <c r="N9" s="2"/>
+      <c r="O9" s="2"/>
+      <c r="P9" s="2"/>
+      <c r="Q9" s="2"/>
+      <c r="R9" s="2"/>
+      <c r="S9" s="2"/>
+      <c r="T9" s="2"/>
+      <c r="U9" s="2"/>
+      <c r="V9" s="2"/>
+      <c r="W9" s="2"/>
+      <c r="X9" s="2"/>
+    </row>
+    <row r="10" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A10" s="2"/>
+      <c r="B10" s="2"/>
+      <c r="C10" s="2"/>
+      <c r="D10" s="2"/>
+      <c r="E10" s="2"/>
+      <c r="F10" s="2"/>
+      <c r="G10" s="2"/>
+      <c r="H10" s="2"/>
+      <c r="I10" s="2"/>
+      <c r="J10" s="2"/>
+      <c r="K10" s="2"/>
+      <c r="L10" s="2"/>
+      <c r="M10" s="2"/>
+      <c r="N10" s="2"/>
+      <c r="O10" s="2"/>
+      <c r="P10" s="2"/>
+      <c r="Q10" s="2"/>
+      <c r="R10" s="2"/>
+      <c r="S10" s="2"/>
+      <c r="T10" s="2"/>
+      <c r="U10" s="2"/>
+      <c r="V10" s="2"/>
+      <c r="W10" s="2"/>
+      <c r="X10" s="2"/>
+    </row>
+    <row r="11" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A11" s="2"/>
+      <c r="B11" s="2"/>
+      <c r="C11" s="2"/>
+      <c r="D11" s="2"/>
+      <c r="E11" s="2"/>
+      <c r="F11" s="2"/>
+      <c r="G11" s="2"/>
+      <c r="H11" s="2"/>
+      <c r="I11" s="2"/>
+      <c r="J11" s="2"/>
+      <c r="K11" s="2"/>
+      <c r="L11" s="2"/>
+      <c r="M11" s="2"/>
+      <c r="N11" s="2"/>
+      <c r="O11" s="2"/>
+      <c r="P11" s="2"/>
+      <c r="Q11" s="2"/>
+      <c r="R11" s="2"/>
+      <c r="S11" s="2"/>
+      <c r="T11" s="2"/>
+      <c r="U11" s="2"/>
+      <c r="V11" s="2"/>
+      <c r="W11" s="2"/>
+      <c r="X11" s="2"/>
+    </row>
+    <row r="12" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A12" s="2"/>
+      <c r="B12" s="2"/>
+      <c r="C12" s="2"/>
+      <c r="D12" s="2"/>
+      <c r="E12" s="2"/>
+      <c r="F12" s="2"/>
+      <c r="G12" s="2"/>
+      <c r="H12" s="2"/>
+      <c r="I12" s="2"/>
+      <c r="J12" s="2"/>
+      <c r="K12" s="2"/>
+      <c r="L12" s="2"/>
+      <c r="M12" s="2"/>
+      <c r="N12" s="2"/>
+      <c r="O12" s="2"/>
+      <c r="P12" s="2"/>
+      <c r="Q12" s="2"/>
+      <c r="R12" s="2"/>
+      <c r="S12" s="2"/>
+      <c r="T12" s="2"/>
+      <c r="U12" s="2"/>
+      <c r="V12" s="2"/>
+      <c r="W12" s="2"/>
+      <c r="X12" s="2"/>
+    </row>
+    <row r="13" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A13" s="2"/>
+      <c r="B13" s="2"/>
+      <c r="C13" s="2"/>
+      <c r="D13" s="2"/>
+      <c r="E13" s="2"/>
+      <c r="F13" s="2"/>
+      <c r="G13" s="2"/>
+      <c r="H13" s="2"/>
+      <c r="I13" s="2"/>
+      <c r="J13" s="2"/>
+      <c r="K13" s="2"/>
+      <c r="L13" s="2"/>
+      <c r="M13" s="2"/>
+      <c r="N13" s="2"/>
+      <c r="O13" s="2"/>
+      <c r="P13" s="2"/>
+      <c r="Q13" s="2"/>
+      <c r="R13" s="2"/>
+      <c r="S13" s="2"/>
+      <c r="T13" s="2"/>
+      <c r="U13" s="2"/>
+      <c r="V13" s="2"/>
+      <c r="W13" s="2"/>
+      <c r="X13" s="2"/>
+    </row>
+    <row r="14" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A14" s="2"/>
+      <c r="B14" s="2"/>
+      <c r="C14" s="2"/>
+      <c r="D14" s="2"/>
+      <c r="E14" s="2"/>
+      <c r="F14" s="2"/>
+      <c r="G14" s="2"/>
+      <c r="H14" s="2"/>
+      <c r="I14" s="2"/>
+      <c r="J14" s="2"/>
+      <c r="K14" s="2"/>
+      <c r="L14" s="2"/>
+      <c r="M14" s="2"/>
+      <c r="N14" s="2"/>
+      <c r="O14" s="2"/>
+      <c r="P14" s="2"/>
+      <c r="Q14" s="2"/>
+      <c r="R14" s="2"/>
+      <c r="S14" s="2"/>
+      <c r="T14" s="2"/>
+      <c r="U14" s="2"/>
+      <c r="V14" s="2"/>
+      <c r="W14" s="2"/>
+      <c r="X14" s="2"/>
+    </row>
+    <row r="15" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A15" s="2"/>
+      <c r="B15" s="2"/>
+      <c r="C15" s="2"/>
+      <c r="D15" s="2"/>
+      <c r="E15" s="2"/>
+      <c r="F15" s="2"/>
+      <c r="G15" s="2"/>
+      <c r="H15" s="2"/>
+      <c r="I15" s="2"/>
+      <c r="J15" s="2"/>
+      <c r="K15" s="2"/>
+      <c r="L15" s="2"/>
+      <c r="M15" s="2"/>
+      <c r="N15" s="2"/>
+      <c r="O15" s="2"/>
+      <c r="P15" s="2"/>
+      <c r="Q15" s="2"/>
+      <c r="R15" s="2"/>
+      <c r="S15" s="2"/>
+      <c r="T15" s="2"/>
+      <c r="U15" s="2"/>
+      <c r="V15" s="2"/>
+      <c r="W15" s="2"/>
+      <c r="X15" s="2"/>
+    </row>
+    <row r="16" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A16" s="2"/>
+      <c r="B16" s="2"/>
+      <c r="C16" s="2"/>
+      <c r="D16" s="2"/>
+      <c r="E16" s="2"/>
+      <c r="F16" s="2"/>
+      <c r="G16" s="2"/>
+      <c r="H16" s="2"/>
+      <c r="I16" s="2"/>
+      <c r="J16" s="2"/>
+      <c r="K16" s="2"/>
+      <c r="L16" s="2"/>
+      <c r="M16" s="2"/>
+      <c r="N16" s="2"/>
+      <c r="O16" s="2"/>
+      <c r="P16" s="2"/>
+      <c r="Q16" s="2"/>
+      <c r="R16" s="2"/>
+      <c r="S16" s="2"/>
+      <c r="T16" s="2"/>
+      <c r="U16" s="2"/>
+      <c r="V16" s="2"/>
+      <c r="W16" s="2"/>
+      <c r="X16" s="2"/>
+    </row>
+    <row r="17" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A17" s="2"/>
+      <c r="B17" s="2"/>
+      <c r="C17" s="2"/>
+      <c r="D17" s="2"/>
+      <c r="E17" s="2"/>
+      <c r="F17" s="2"/>
+      <c r="G17" s="2"/>
+      <c r="H17" s="2"/>
+      <c r="I17" s="2"/>
+      <c r="J17" s="2"/>
+      <c r="K17" s="2"/>
+      <c r="L17" s="2"/>
+      <c r="M17" s="2"/>
+      <c r="N17" s="2"/>
+      <c r="O17" s="2"/>
+      <c r="P17" s="2"/>
+      <c r="Q17" s="2"/>
+      <c r="R17" s="2"/>
+      <c r="S17" s="2"/>
+      <c r="T17" s="2"/>
+      <c r="U17" s="2"/>
+      <c r="V17" s="2"/>
+      <c r="W17" s="2"/>
+      <c r="X17" s="2"/>
+    </row>
+    <row r="18" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A18" s="2"/>
+      <c r="B18" s="2"/>
+      <c r="C18" s="2"/>
+      <c r="D18" s="2"/>
+      <c r="E18" s="2"/>
+      <c r="F18" s="2"/>
+      <c r="G18" s="2"/>
+      <c r="H18" s="2"/>
+      <c r="I18" s="2"/>
+      <c r="J18" s="2"/>
+      <c r="K18" s="2"/>
+      <c r="L18" s="2"/>
+      <c r="M18" s="2"/>
+      <c r="N18" s="2"/>
+      <c r="O18" s="2"/>
+      <c r="P18" s="2"/>
+      <c r="Q18" s="2"/>
+      <c r="R18" s="2"/>
+      <c r="S18" s="2"/>
+      <c r="T18" s="2"/>
+      <c r="U18" s="2"/>
+      <c r="V18" s="2"/>
+      <c r="W18" s="2"/>
+      <c r="X18" s="2"/>
+    </row>
+    <row r="19" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A19" s="2"/>
+      <c r="B19" s="2"/>
+      <c r="C19" s="2"/>
+      <c r="D19" s="2"/>
+      <c r="E19" s="2"/>
+      <c r="F19" s="2"/>
+      <c r="G19" s="2"/>
+      <c r="H19" s="2"/>
+      <c r="I19" s="2"/>
+      <c r="J19" s="2"/>
+      <c r="K19" s="2"/>
+      <c r="L19" s="2"/>
+      <c r="M19" s="2"/>
+      <c r="N19" s="2"/>
+      <c r="O19" s="2"/>
+      <c r="P19" s="2"/>
+      <c r="Q19" s="2"/>
+      <c r="R19" s="2"/>
+      <c r="S19" s="2"/>
+      <c r="T19" s="2"/>
+      <c r="U19" s="2"/>
+      <c r="V19" s="2"/>
+      <c r="W19" s="2"/>
+      <c r="X19" s="2"/>
+    </row>
+    <row r="20" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A20" s="2"/>
+      <c r="B20" s="2"/>
+      <c r="C20" s="2"/>
+      <c r="D20" s="2"/>
+      <c r="E20" s="2"/>
+      <c r="F20" s="2"/>
+      <c r="G20" s="2"/>
+      <c r="H20" s="2"/>
+      <c r="I20" s="2"/>
+      <c r="J20" s="2"/>
+      <c r="K20" s="2"/>
+      <c r="L20" s="2"/>
+      <c r="M20" s="2"/>
+      <c r="N20" s="2"/>
+      <c r="O20" s="2"/>
+      <c r="P20" s="2"/>
+      <c r="Q20" s="2"/>
+      <c r="R20" s="2"/>
+      <c r="S20" s="2"/>
+      <c r="T20" s="2"/>
+      <c r="U20" s="2"/>
+      <c r="V20" s="2"/>
+      <c r="W20" s="2"/>
+      <c r="X20" s="2"/>
+    </row>
+    <row r="21" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A21" s="2"/>
+      <c r="B21" s="2"/>
+      <c r="C21" s="2"/>
+      <c r="D21" s="2"/>
+      <c r="E21" s="2"/>
+      <c r="F21" s="2"/>
+      <c r="G21" s="2"/>
+      <c r="H21" s="2"/>
+      <c r="I21" s="2"/>
+      <c r="J21" s="2"/>
+      <c r="K21" s="2"/>
+      <c r="L21" s="2"/>
+      <c r="M21" s="2"/>
+      <c r="N21" s="2"/>
+      <c r="O21" s="2"/>
+      <c r="P21" s="2"/>
+      <c r="Q21" s="2"/>
+      <c r="R21" s="2"/>
+      <c r="S21" s="2"/>
+      <c r="T21" s="2"/>
+      <c r="U21" s="2"/>
+      <c r="V21" s="2"/>
+      <c r="W21" s="2"/>
+      <c r="X21" s="2"/>
+    </row>
+    <row r="22" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A22" s="2"/>
+      <c r="B22" s="2"/>
+      <c r="C22" s="2"/>
+      <c r="D22" s="2"/>
+      <c r="E22" s="2"/>
+      <c r="F22" s="2"/>
+      <c r="G22" s="2"/>
+      <c r="H22" s="2"/>
+      <c r="I22" s="2"/>
+      <c r="J22" s="2"/>
+      <c r="K22" s="2"/>
+      <c r="L22" s="2"/>
+      <c r="M22" s="2"/>
+      <c r="N22" s="2"/>
+      <c r="O22" s="2"/>
+      <c r="P22" s="2"/>
+      <c r="Q22" s="2"/>
+      <c r="R22" s="2"/>
+      <c r="S22" s="2"/>
+      <c r="T22" s="2"/>
+      <c r="U22" s="2"/>
+      <c r="V22" s="2"/>
+      <c r="W22" s="2"/>
+      <c r="X22" s="2"/>
+    </row>
+    <row r="23" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A23" s="2"/>
+      <c r="B23" s="2"/>
+      <c r="C23" s="2"/>
+      <c r="D23" s="2"/>
+      <c r="E23" s="2"/>
+      <c r="F23" s="2"/>
+      <c r="G23" s="2"/>
+      <c r="H23" s="2"/>
+      <c r="I23" s="2"/>
+      <c r="J23" s="2"/>
+      <c r="K23" s="2"/>
+      <c r="L23" s="2"/>
+      <c r="M23" s="2"/>
+      <c r="N23" s="2"/>
+      <c r="O23" s="2"/>
+      <c r="P23" s="2"/>
+      <c r="Q23" s="2"/>
+      <c r="R23" s="2"/>
+      <c r="S23" s="2"/>
+      <c r="T23" s="2"/>
+      <c r="U23" s="2"/>
+      <c r="V23" s="2"/>
+      <c r="W23" s="2"/>
+      <c r="X23" s="2"/>
+    </row>
+    <row r="24" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A24" s="2"/>
+      <c r="B24" s="2"/>
+      <c r="C24" s="2"/>
+      <c r="D24" s="2"/>
+      <c r="E24" s="2"/>
+      <c r="F24" s="2"/>
+      <c r="G24" s="2"/>
+      <c r="H24" s="2"/>
+      <c r="I24" s="2"/>
+      <c r="J24" s="2"/>
+      <c r="K24" s="2"/>
+      <c r="L24" s="2"/>
+      <c r="M24" s="2"/>
+      <c r="N24" s="2"/>
+      <c r="O24" s="2"/>
+      <c r="P24" s="2"/>
+      <c r="Q24" s="2"/>
+      <c r="R24" s="2"/>
+      <c r="S24" s="2"/>
+      <c r="T24" s="2"/>
+      <c r="U24" s="2"/>
+      <c r="V24" s="2"/>
+      <c r="W24" s="2"/>
+      <c r="X24" s="2"/>
+    </row>
+    <row r="25" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A25" s="2"/>
+      <c r="B25" s="2"/>
+      <c r="C25" s="2"/>
+      <c r="D25" s="2"/>
+      <c r="E25" s="2"/>
+      <c r="F25" s="2"/>
+      <c r="G25" s="2"/>
+      <c r="H25" s="2"/>
+      <c r="I25" s="2"/>
+      <c r="J25" s="2"/>
+      <c r="K25" s="2"/>
+      <c r="L25" s="2"/>
+      <c r="M25" s="2"/>
+      <c r="N25" s="2"/>
+      <c r="O25" s="2"/>
+      <c r="P25" s="2"/>
+      <c r="Q25" s="2"/>
+      <c r="R25" s="2"/>
+      <c r="S25" s="2"/>
+      <c r="T25" s="2"/>
+      <c r="U25" s="2"/>
+      <c r="V25" s="2"/>
+      <c r="W25" s="2"/>
+      <c r="X25" s="2"/>
+    </row>
+    <row r="26" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A26" s="2"/>
+      <c r="B26" s="2"/>
+      <c r="C26" s="2"/>
+      <c r="D26" s="2"/>
+      <c r="E26" s="2"/>
+      <c r="F26" s="2"/>
+      <c r="G26" s="2"/>
+      <c r="H26" s="2"/>
+      <c r="I26" s="2"/>
+      <c r="J26" s="2"/>
+      <c r="K26" s="2"/>
+      <c r="L26" s="2"/>
+      <c r="M26" s="2"/>
+      <c r="N26" s="2"/>
+      <c r="O26" s="2"/>
+      <c r="P26" s="2"/>
+      <c r="Q26" s="2"/>
+      <c r="R26" s="2"/>
+      <c r="S26" s="2"/>
+      <c r="T26" s="2"/>
+      <c r="U26" s="2"/>
+      <c r="V26" s="2"/>
+      <c r="W26" s="2"/>
+      <c r="X26" s="2"/>
+    </row>
+    <row r="27" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A27" s="2"/>
+      <c r="B27" s="2"/>
+      <c r="C27" s="2"/>
+      <c r="D27" s="2"/>
+      <c r="E27" s="2"/>
+      <c r="F27" s="2"/>
+      <c r="G27" s="2"/>
+      <c r="H27" s="2"/>
+      <c r="I27" s="2"/>
+      <c r="J27" s="2"/>
+      <c r="K27" s="2"/>
+      <c r="L27" s="2"/>
+      <c r="M27" s="2"/>
+      <c r="N27" s="2"/>
+      <c r="O27" s="2"/>
+      <c r="P27" s="2"/>
+      <c r="Q27" s="2"/>
+      <c r="R27" s="2"/>
+      <c r="S27" s="2"/>
+      <c r="T27" s="2"/>
+      <c r="U27" s="2"/>
+      <c r="V27" s="2"/>
+      <c r="W27" s="2"/>
+      <c r="X27" s="2"/>
+    </row>
+    <row r="28" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A28" s="2"/>
+      <c r="B28" s="2"/>
+      <c r="C28" s="2"/>
+      <c r="D28" s="2"/>
+      <c r="E28" s="2"/>
+      <c r="F28" s="2"/>
+      <c r="G28" s="2"/>
+      <c r="H28" s="2"/>
+      <c r="I28" s="2"/>
+      <c r="J28" s="2"/>
+      <c r="K28" s="2"/>
+      <c r="L28" s="2"/>
+      <c r="M28" s="2"/>
+      <c r="N28" s="2"/>
+      <c r="O28" s="2"/>
+      <c r="P28" s="2"/>
+      <c r="Q28" s="2"/>
+      <c r="R28" s="2"/>
+      <c r="S28" s="2"/>
+      <c r="T28" s="2"/>
+      <c r="U28" s="2"/>
+      <c r="V28" s="2"/>
+      <c r="W28" s="2"/>
+      <c r="X28" s="2"/>
+    </row>
+    <row r="29" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A29" s="2"/>
+      <c r="B29" s="2"/>
+      <c r="C29" s="2"/>
+      <c r="D29" s="2"/>
+      <c r="E29" s="2"/>
+      <c r="F29" s="2"/>
+      <c r="G29" s="2"/>
+      <c r="H29" s="2"/>
+      <c r="I29" s="2"/>
+      <c r="J29" s="2"/>
+      <c r="K29" s="2"/>
+      <c r="L29" s="2"/>
+      <c r="M29" s="2"/>
+      <c r="N29" s="2"/>
+      <c r="O29" s="2"/>
+      <c r="P29" s="2"/>
+      <c r="Q29" s="2"/>
+      <c r="R29" s="2"/>
+      <c r="S29" s="2"/>
+      <c r="T29" s="2"/>
+      <c r="U29" s="2"/>
+      <c r="V29" s="2"/>
+      <c r="W29" s="2"/>
+      <c r="X29" s="2"/>
+    </row>
+    <row r="30" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A30" s="2"/>
+      <c r="B30" s="2"/>
+      <c r="C30" s="2"/>
+      <c r="D30" s="2"/>
+      <c r="E30" s="2"/>
+      <c r="F30" s="2"/>
+      <c r="G30" s="2"/>
+      <c r="H30" s="2"/>
+      <c r="I30" s="2"/>
+      <c r="J30" s="2"/>
+      <c r="K30" s="2"/>
+      <c r="L30" s="2"/>
+      <c r="M30" s="2"/>
+      <c r="N30" s="2"/>
+      <c r="O30" s="2"/>
+      <c r="P30" s="2"/>
+      <c r="Q30" s="2"/>
+      <c r="R30" s="2"/>
+      <c r="S30" s="2"/>
+      <c r="T30" s="2"/>
+      <c r="U30" s="2"/>
+      <c r="V30" s="2"/>
+      <c r="W30" s="2"/>
+      <c r="X30" s="2"/>
+    </row>
+    <row r="31" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A31" s="2"/>
+      <c r="B31" s="2"/>
+      <c r="C31" s="2"/>
+      <c r="D31" s="2"/>
+      <c r="E31" s="2"/>
+      <c r="F31" s="2"/>
+      <c r="G31" s="2"/>
+      <c r="H31" s="2"/>
+      <c r="I31" s="2"/>
+      <c r="J31" s="2"/>
+      <c r="K31" s="2"/>
+      <c r="L31" s="2"/>
+      <c r="M31" s="2"/>
+      <c r="N31" s="2"/>
+      <c r="O31" s="2"/>
+      <c r="P31" s="2"/>
+      <c r="Q31" s="2"/>
+      <c r="R31" s="2"/>
+      <c r="S31" s="2"/>
+      <c r="T31" s="2"/>
+      <c r="U31" s="2"/>
+      <c r="V31" s="2"/>
+      <c r="W31" s="2"/>
+      <c r="X31" s="2"/>
+    </row>
+    <row r="32" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A32" s="2"/>
+      <c r="B32" s="2"/>
+      <c r="C32" s="2"/>
+      <c r="D32" s="2"/>
+      <c r="E32" s="2"/>
+      <c r="F32" s="2"/>
+      <c r="G32" s="2"/>
+      <c r="H32" s="2"/>
+      <c r="I32" s="2"/>
+      <c r="J32" s="2"/>
+      <c r="K32" s="2"/>
+      <c r="L32" s="2"/>
+      <c r="M32" s="2"/>
+      <c r="N32" s="2"/>
+      <c r="O32" s="2"/>
+      <c r="P32" s="2"/>
+      <c r="Q32" s="2"/>
+      <c r="R32" s="2"/>
+      <c r="S32" s="2"/>
+      <c r="T32" s="2"/>
+      <c r="U32" s="2"/>
+      <c r="V32" s="2"/>
+      <c r="W32" s="2"/>
+      <c r="X32" s="2"/>
+    </row>
+    <row r="33" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A33" s="2"/>
+      <c r="B33" s="2"/>
+      <c r="C33" s="2"/>
+      <c r="D33" s="2"/>
+      <c r="E33" s="2"/>
+      <c r="F33" s="2"/>
+      <c r="G33" s="2"/>
+      <c r="H33" s="2"/>
+      <c r="I33" s="2"/>
+      <c r="J33" s="2"/>
+      <c r="K33" s="2"/>
+      <c r="L33" s="2"/>
+      <c r="M33" s="2"/>
+      <c r="N33" s="2"/>
+      <c r="O33" s="2"/>
+      <c r="P33" s="2"/>
+      <c r="Q33" s="2"/>
+      <c r="R33" s="2"/>
+      <c r="S33" s="2"/>
+      <c r="T33" s="2"/>
+      <c r="U33" s="2"/>
+      <c r="V33" s="2"/>
+      <c r="W33" s="2"/>
+      <c r="X33" s="2"/>
+    </row>
+    <row r="34" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A34" s="2"/>
+      <c r="B34" s="2"/>
+      <c r="C34" s="2"/>
+      <c r="D34" s="2"/>
+      <c r="E34" s="2"/>
+      <c r="F34" s="2"/>
+      <c r="G34" s="2"/>
+      <c r="H34" s="2"/>
+      <c r="I34" s="2"/>
+      <c r="J34" s="2"/>
+      <c r="K34" s="2"/>
+      <c r="L34" s="2"/>
+      <c r="M34" s="2"/>
+      <c r="N34" s="2"/>
+      <c r="O34" s="2"/>
+      <c r="P34" s="2"/>
+      <c r="Q34" s="2"/>
+      <c r="R34" s="2"/>
+      <c r="S34" s="2"/>
+      <c r="T34" s="2"/>
+      <c r="U34" s="2"/>
+      <c r="V34" s="2"/>
+      <c r="W34" s="2"/>
+      <c r="X34" s="2"/>
+    </row>
+    <row r="35" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A35" s="2"/>
+      <c r="B35" s="2"/>
+      <c r="C35" s="2"/>
+      <c r="D35" s="2"/>
+      <c r="E35" s="2"/>
+      <c r="F35" s="2"/>
+      <c r="G35" s="2"/>
+      <c r="H35" s="2"/>
+      <c r="I35" s="2"/>
+      <c r="J35" s="2"/>
+      <c r="K35" s="2"/>
+      <c r="L35" s="2"/>
+      <c r="M35" s="2"/>
+      <c r="N35" s="2"/>
+      <c r="O35" s="2"/>
+      <c r="P35" s="2"/>
+      <c r="Q35" s="2"/>
+      <c r="R35" s="2"/>
+      <c r="S35" s="2"/>
+      <c r="T35" s="2"/>
+      <c r="U35" s="2"/>
+      <c r="V35" s="2"/>
+      <c r="W35" s="2"/>
+      <c r="X35" s="2"/>
+    </row>
+    <row r="36" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A36" s="2"/>
+      <c r="B36" s="2"/>
+      <c r="C36" s="2"/>
+      <c r="D36" s="2"/>
+      <c r="E36" s="2"/>
+      <c r="F36" s="2"/>
+      <c r="G36" s="2"/>
+      <c r="H36" s="2"/>
+      <c r="I36" s="2"/>
+      <c r="J36" s="2"/>
+      <c r="K36" s="2"/>
+      <c r="L36" s="2"/>
+      <c r="M36" s="2"/>
+      <c r="N36" s="2"/>
+      <c r="O36" s="2"/>
+      <c r="P36" s="2"/>
+      <c r="Q36" s="2"/>
+      <c r="R36" s="2"/>
+      <c r="S36" s="2"/>
+      <c r="T36" s="2"/>
+      <c r="U36" s="2"/>
+      <c r="V36" s="2"/>
+      <c r="W36" s="2"/>
+      <c r="X36" s="2"/>
+    </row>
+    <row r="37" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A37" s="2"/>
+      <c r="B37" s="2"/>
+      <c r="C37" s="2"/>
+      <c r="D37" s="2"/>
+      <c r="E37" s="2"/>
+      <c r="F37" s="2"/>
+      <c r="G37" s="2"/>
+      <c r="H37" s="2"/>
+      <c r="I37" s="2"/>
+      <c r="J37" s="2"/>
+      <c r="K37" s="2"/>
+      <c r="L37" s="2"/>
+      <c r="M37" s="2"/>
+      <c r="N37" s="2"/>
+      <c r="O37" s="2"/>
+      <c r="P37" s="2"/>
+      <c r="Q37" s="2"/>
+      <c r="R37" s="2"/>
+      <c r="S37" s="2"/>
+      <c r="T37" s="2"/>
+      <c r="U37" s="2"/>
+      <c r="V37" s="2"/>
+      <c r="W37" s="2"/>
+      <c r="X37" s="2"/>
+    </row>
+    <row r="38" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A38" s="2"/>
+      <c r="B38" s="2"/>
+      <c r="C38" s="2"/>
+      <c r="D38" s="2"/>
+      <c r="E38" s="2"/>
+      <c r="F38" s="2"/>
+      <c r="G38" s="2"/>
+      <c r="H38" s="2"/>
+      <c r="I38" s="2"/>
+      <c r="J38" s="2"/>
+      <c r="K38" s="2"/>
+      <c r="L38" s="2"/>
+      <c r="M38" s="2"/>
+      <c r="N38" s="2"/>
+      <c r="O38" s="2"/>
+      <c r="P38" s="2"/>
+      <c r="Q38" s="2"/>
+      <c r="R38" s="2"/>
+      <c r="S38" s="2"/>
+      <c r="T38" s="2"/>
+      <c r="U38" s="2"/>
+      <c r="V38" s="2"/>
+      <c r="W38" s="2"/>
+      <c r="X38" s="2"/>
+    </row>
+    <row r="39" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A39" s="2"/>
+      <c r="B39" s="2"/>
+      <c r="C39" s="2"/>
+      <c r="D39" s="2"/>
+      <c r="E39" s="2"/>
+      <c r="F39" s="2"/>
+      <c r="G39" s="2"/>
+      <c r="H39" s="2"/>
+      <c r="I39" s="2"/>
+      <c r="J39" s="2"/>
+      <c r="K39" s="2"/>
+      <c r="L39" s="2"/>
+      <c r="M39" s="2"/>
+      <c r="N39" s="2"/>
+      <c r="O39" s="2"/>
+      <c r="P39" s="2"/>
+      <c r="Q39" s="2"/>
+      <c r="R39" s="2"/>
+      <c r="S39" s="2"/>
+      <c r="T39" s="2"/>
+      <c r="U39" s="2"/>
+      <c r="V39" s="2"/>
+      <c r="W39" s="2"/>
+      <c r="X39" s="2"/>
+    </row>
+    <row r="40" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A40" s="2"/>
+      <c r="B40" s="2"/>
+      <c r="C40" s="2"/>
+      <c r="D40" s="2"/>
+      <c r="E40" s="2"/>
+      <c r="F40" s="2"/>
+      <c r="G40" s="2"/>
+      <c r="H40" s="2"/>
+      <c r="I40" s="2"/>
+      <c r="J40" s="2"/>
+      <c r="K40" s="2"/>
+      <c r="L40" s="2"/>
+      <c r="M40" s="2"/>
+      <c r="N40" s="2"/>
+      <c r="O40" s="2"/>
+      <c r="P40" s="2"/>
+      <c r="Q40" s="2"/>
+      <c r="R40" s="2"/>
+      <c r="S40" s="2"/>
+      <c r="T40" s="2"/>
+      <c r="U40" s="2"/>
+      <c r="V40" s="2"/>
+      <c r="W40" s="2"/>
+      <c r="X40" s="2"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -543,35 +1597,1071 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:B3"/>
+  <dimension ref="A1:X40"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
-    <col min="1" max="24" width="13.571428571428571" customWidth="1"/>
+    <col min="1" max="2" width="13.571428571428571" customWidth="1"/>
+    <col min="3" max="3" width="16.857142857142858" customWidth="1"/>
+    <col min="4" max="24" width="13.571428571428571" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A1" t="s">
+    <row r="1" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>13</v>
-      </c>
-      <c r="B2">
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1"/>
+      <c r="E1" s="1"/>
+      <c r="F1" s="1"/>
+      <c r="G1" s="1"/>
+      <c r="H1" s="1"/>
+      <c r="I1" s="1"/>
+      <c r="J1" s="1"/>
+      <c r="K1" s="1"/>
+      <c r="L1" s="1"/>
+      <c r="M1" s="1"/>
+      <c r="N1" s="1"/>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+      <c r="T1" s="1"/>
+      <c r="U1" s="1"/>
+      <c r="V1" s="1"/>
+      <c r="W1" s="1"/>
+      <c r="X1" s="1"/>
+    </row>
+    <row r="2" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A2" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="B2" s="2">
         <v>4028609</v>
       </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>14</v>
-      </c>
-      <c r="B3" t="s">
-        <v>15</v>
-      </c>
+      <c r="C2" s="2">
+        <v>4028619</v>
+      </c>
+      <c r="D2" s="2"/>
+      <c r="E2" s="2"/>
+      <c r="F2" s="2"/>
+      <c r="G2" s="2"/>
+      <c r="H2" s="2"/>
+      <c r="I2" s="2"/>
+      <c r="J2" s="2"/>
+      <c r="K2" s="2"/>
+      <c r="L2" s="2"/>
+      <c r="M2" s="2"/>
+      <c r="N2" s="2"/>
+      <c r="O2" s="2"/>
+      <c r="P2" s="2"/>
+      <c r="Q2" s="2"/>
+      <c r="R2" s="2"/>
+      <c r="S2" s="2"/>
+      <c r="T2" s="2"/>
+      <c r="U2" s="2"/>
+      <c r="V2" s="2"/>
+      <c r="W2" s="2"/>
+      <c r="X2" s="2"/>
+    </row>
+    <row r="3" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A3" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D3" s="2"/>
+      <c r="E3" s="2"/>
+      <c r="F3" s="2"/>
+      <c r="G3" s="2"/>
+      <c r="H3" s="2"/>
+      <c r="I3" s="2"/>
+      <c r="J3" s="2"/>
+      <c r="K3" s="2"/>
+      <c r="L3" s="2"/>
+      <c r="M3" s="2"/>
+      <c r="N3" s="2"/>
+      <c r="O3" s="2"/>
+      <c r="P3" s="2"/>
+      <c r="Q3" s="2"/>
+      <c r="R3" s="2"/>
+      <c r="S3" s="2"/>
+      <c r="T3" s="2"/>
+      <c r="U3" s="2"/>
+      <c r="V3" s="2"/>
+      <c r="W3" s="2"/>
+      <c r="X3" s="2"/>
+    </row>
+    <row r="4" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A4" s="2"/>
+      <c r="B4" s="2"/>
+      <c r="C4" s="2"/>
+      <c r="D4" s="2"/>
+      <c r="E4" s="2"/>
+      <c r="F4" s="2"/>
+      <c r="G4" s="2"/>
+      <c r="H4" s="2"/>
+      <c r="I4" s="2"/>
+      <c r="J4" s="2"/>
+      <c r="K4" s="2"/>
+      <c r="L4" s="2"/>
+      <c r="M4" s="2"/>
+      <c r="N4" s="2"/>
+      <c r="O4" s="2"/>
+      <c r="P4" s="2"/>
+      <c r="Q4" s="2"/>
+      <c r="R4" s="2"/>
+      <c r="S4" s="2"/>
+      <c r="T4" s="2"/>
+      <c r="U4" s="2"/>
+      <c r="V4" s="2"/>
+      <c r="W4" s="2"/>
+      <c r="X4" s="2"/>
+    </row>
+    <row r="5" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A5" s="2"/>
+      <c r="B5" s="2"/>
+      <c r="C5" s="2"/>
+      <c r="D5" s="2"/>
+      <c r="E5" s="2"/>
+      <c r="F5" s="2"/>
+      <c r="G5" s="2"/>
+      <c r="H5" s="2"/>
+      <c r="I5" s="2"/>
+      <c r="J5" s="2"/>
+      <c r="K5" s="2"/>
+      <c r="L5" s="2"/>
+      <c r="M5" s="2"/>
+      <c r="N5" s="2"/>
+      <c r="O5" s="2"/>
+      <c r="P5" s="2"/>
+      <c r="Q5" s="2"/>
+      <c r="R5" s="2"/>
+      <c r="S5" s="2"/>
+      <c r="T5" s="2"/>
+      <c r="U5" s="2"/>
+      <c r="V5" s="2"/>
+      <c r="W5" s="2"/>
+      <c r="X5" s="2"/>
+    </row>
+    <row r="6" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A6" s="2"/>
+      <c r="B6" s="2"/>
+      <c r="C6" s="2"/>
+      <c r="D6" s="2"/>
+      <c r="E6" s="2"/>
+      <c r="F6" s="2"/>
+      <c r="G6" s="2"/>
+      <c r="H6" s="2"/>
+      <c r="I6" s="2"/>
+      <c r="J6" s="2"/>
+      <c r="K6" s="2"/>
+      <c r="L6" s="2"/>
+      <c r="M6" s="2"/>
+      <c r="N6" s="2"/>
+      <c r="O6" s="2"/>
+      <c r="P6" s="2"/>
+      <c r="Q6" s="2"/>
+      <c r="R6" s="2"/>
+      <c r="S6" s="2"/>
+      <c r="T6" s="2"/>
+      <c r="U6" s="2"/>
+      <c r="V6" s="2"/>
+      <c r="W6" s="2"/>
+      <c r="X6" s="2"/>
+    </row>
+    <row r="7" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A7" s="2"/>
+      <c r="B7" s="2"/>
+      <c r="C7" s="2"/>
+      <c r="D7" s="2"/>
+      <c r="E7" s="2"/>
+      <c r="F7" s="2"/>
+      <c r="G7" s="2"/>
+      <c r="H7" s="2"/>
+      <c r="I7" s="2"/>
+      <c r="J7" s="2"/>
+      <c r="K7" s="2"/>
+      <c r="L7" s="2"/>
+      <c r="M7" s="2"/>
+      <c r="N7" s="2"/>
+      <c r="O7" s="2"/>
+      <c r="P7" s="2"/>
+      <c r="Q7" s="2"/>
+      <c r="R7" s="2"/>
+      <c r="S7" s="2"/>
+      <c r="T7" s="2"/>
+      <c r="U7" s="2"/>
+      <c r="V7" s="2"/>
+      <c r="W7" s="2"/>
+      <c r="X7" s="2"/>
+    </row>
+    <row r="8" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A8" s="2"/>
+      <c r="B8" s="2"/>
+      <c r="C8" s="2"/>
+      <c r="D8" s="2"/>
+      <c r="E8" s="2"/>
+      <c r="F8" s="2"/>
+      <c r="G8" s="2"/>
+      <c r="H8" s="2"/>
+      <c r="I8" s="2"/>
+      <c r="J8" s="2"/>
+      <c r="K8" s="2"/>
+      <c r="L8" s="2"/>
+      <c r="M8" s="2"/>
+      <c r="N8" s="2"/>
+      <c r="O8" s="2"/>
+      <c r="P8" s="2"/>
+      <c r="Q8" s="2"/>
+      <c r="R8" s="2"/>
+      <c r="S8" s="2"/>
+      <c r="T8" s="2"/>
+      <c r="U8" s="2"/>
+      <c r="V8" s="2"/>
+      <c r="W8" s="2"/>
+      <c r="X8" s="2"/>
+    </row>
+    <row r="9" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A9" s="2"/>
+      <c r="B9" s="2"/>
+      <c r="C9" s="2"/>
+      <c r="D9" s="2"/>
+      <c r="E9" s="2"/>
+      <c r="F9" s="2"/>
+      <c r="G9" s="2"/>
+      <c r="H9" s="2"/>
+      <c r="I9" s="2"/>
+      <c r="J9" s="2"/>
+      <c r="K9" s="2"/>
+      <c r="L9" s="2"/>
+      <c r="M9" s="2"/>
+      <c r="N9" s="2"/>
+      <c r="O9" s="2"/>
+      <c r="P9" s="2"/>
+      <c r="Q9" s="2"/>
+      <c r="R9" s="2"/>
+      <c r="S9" s="2"/>
+      <c r="T9" s="2"/>
+      <c r="U9" s="2"/>
+      <c r="V9" s="2"/>
+      <c r="W9" s="2"/>
+      <c r="X9" s="2"/>
+    </row>
+    <row r="10" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A10" s="2"/>
+      <c r="B10" s="2"/>
+      <c r="C10" s="2"/>
+      <c r="D10" s="2"/>
+      <c r="E10" s="2"/>
+      <c r="F10" s="2"/>
+      <c r="G10" s="2"/>
+      <c r="H10" s="2"/>
+      <c r="I10" s="2"/>
+      <c r="J10" s="2"/>
+      <c r="K10" s="2"/>
+      <c r="L10" s="2"/>
+      <c r="M10" s="2"/>
+      <c r="N10" s="2"/>
+      <c r="O10" s="2"/>
+      <c r="P10" s="2"/>
+      <c r="Q10" s="2"/>
+      <c r="R10" s="2"/>
+      <c r="S10" s="2"/>
+      <c r="T10" s="2"/>
+      <c r="U10" s="2"/>
+      <c r="V10" s="2"/>
+      <c r="W10" s="2"/>
+      <c r="X10" s="2"/>
+    </row>
+    <row r="11" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A11" s="2"/>
+      <c r="B11" s="2"/>
+      <c r="C11" s="2"/>
+      <c r="D11" s="2"/>
+      <c r="E11" s="2"/>
+      <c r="F11" s="2"/>
+      <c r="G11" s="2"/>
+      <c r="H11" s="2"/>
+      <c r="I11" s="2"/>
+      <c r="J11" s="2"/>
+      <c r="K11" s="2"/>
+      <c r="L11" s="2"/>
+      <c r="M11" s="2"/>
+      <c r="N11" s="2"/>
+      <c r="O11" s="2"/>
+      <c r="P11" s="2"/>
+      <c r="Q11" s="2"/>
+      <c r="R11" s="2"/>
+      <c r="S11" s="2"/>
+      <c r="T11" s="2"/>
+      <c r="U11" s="2"/>
+      <c r="V11" s="2"/>
+      <c r="W11" s="2"/>
+      <c r="X11" s="2"/>
+    </row>
+    <row r="12" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A12" s="2"/>
+      <c r="B12" s="2"/>
+      <c r="C12" s="2"/>
+      <c r="D12" s="2"/>
+      <c r="E12" s="2"/>
+      <c r="F12" s="2"/>
+      <c r="G12" s="2"/>
+      <c r="H12" s="2"/>
+      <c r="I12" s="2"/>
+      <c r="J12" s="2"/>
+      <c r="K12" s="2"/>
+      <c r="L12" s="2"/>
+      <c r="M12" s="2"/>
+      <c r="N12" s="2"/>
+      <c r="O12" s="2"/>
+      <c r="P12" s="2"/>
+      <c r="Q12" s="2"/>
+      <c r="R12" s="2"/>
+      <c r="S12" s="2"/>
+      <c r="T12" s="2"/>
+      <c r="U12" s="2"/>
+      <c r="V12" s="2"/>
+      <c r="W12" s="2"/>
+      <c r="X12" s="2"/>
+    </row>
+    <row r="13" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A13" s="2"/>
+      <c r="B13" s="2"/>
+      <c r="C13" s="2"/>
+      <c r="D13" s="2"/>
+      <c r="E13" s="2"/>
+      <c r="F13" s="2"/>
+      <c r="G13" s="2"/>
+      <c r="H13" s="2"/>
+      <c r="I13" s="2"/>
+      <c r="J13" s="2"/>
+      <c r="K13" s="2"/>
+      <c r="L13" s="2"/>
+      <c r="M13" s="2"/>
+      <c r="N13" s="2"/>
+      <c r="O13" s="2"/>
+      <c r="P13" s="2"/>
+      <c r="Q13" s="2"/>
+      <c r="R13" s="2"/>
+      <c r="S13" s="2"/>
+      <c r="T13" s="2"/>
+      <c r="U13" s="2"/>
+      <c r="V13" s="2"/>
+      <c r="W13" s="2"/>
+      <c r="X13" s="2"/>
+    </row>
+    <row r="14" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A14" s="2"/>
+      <c r="B14" s="2"/>
+      <c r="C14" s="2"/>
+      <c r="D14" s="2"/>
+      <c r="E14" s="2"/>
+      <c r="F14" s="2"/>
+      <c r="G14" s="2"/>
+      <c r="H14" s="2"/>
+      <c r="I14" s="2"/>
+      <c r="J14" s="2"/>
+      <c r="K14" s="2"/>
+      <c r="L14" s="2"/>
+      <c r="M14" s="2"/>
+      <c r="N14" s="2"/>
+      <c r="O14" s="2"/>
+      <c r="P14" s="2"/>
+      <c r="Q14" s="2"/>
+      <c r="R14" s="2"/>
+      <c r="S14" s="2"/>
+      <c r="T14" s="2"/>
+      <c r="U14" s="2"/>
+      <c r="V14" s="2"/>
+      <c r="W14" s="2"/>
+      <c r="X14" s="2"/>
+    </row>
+    <row r="15" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A15" s="2"/>
+      <c r="B15" s="2"/>
+      <c r="C15" s="2"/>
+      <c r="D15" s="2"/>
+      <c r="E15" s="2"/>
+      <c r="F15" s="2"/>
+      <c r="G15" s="2"/>
+      <c r="H15" s="2"/>
+      <c r="I15" s="2"/>
+      <c r="J15" s="2"/>
+      <c r="K15" s="2"/>
+      <c r="L15" s="2"/>
+      <c r="M15" s="2"/>
+      <c r="N15" s="2"/>
+      <c r="O15" s="2"/>
+      <c r="P15" s="2"/>
+      <c r="Q15" s="2"/>
+      <c r="R15" s="2"/>
+      <c r="S15" s="2"/>
+      <c r="T15" s="2"/>
+      <c r="U15" s="2"/>
+      <c r="V15" s="2"/>
+      <c r="W15" s="2"/>
+      <c r="X15" s="2"/>
+    </row>
+    <row r="16" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A16" s="2"/>
+      <c r="B16" s="2"/>
+      <c r="C16" s="2"/>
+      <c r="D16" s="2"/>
+      <c r="E16" s="2"/>
+      <c r="F16" s="2"/>
+      <c r="G16" s="2"/>
+      <c r="H16" s="2"/>
+      <c r="I16" s="2"/>
+      <c r="J16" s="2"/>
+      <c r="K16" s="2"/>
+      <c r="L16" s="2"/>
+      <c r="M16" s="2"/>
+      <c r="N16" s="2"/>
+      <c r="O16" s="2"/>
+      <c r="P16" s="2"/>
+      <c r="Q16" s="2"/>
+      <c r="R16" s="2"/>
+      <c r="S16" s="2"/>
+      <c r="T16" s="2"/>
+      <c r="U16" s="2"/>
+      <c r="V16" s="2"/>
+      <c r="W16" s="2"/>
+      <c r="X16" s="2"/>
+    </row>
+    <row r="17" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A17" s="2"/>
+      <c r="B17" s="2"/>
+      <c r="C17" s="2"/>
+      <c r="D17" s="2"/>
+      <c r="E17" s="2"/>
+      <c r="F17" s="2"/>
+      <c r="G17" s="2"/>
+      <c r="H17" s="2"/>
+      <c r="I17" s="2"/>
+      <c r="J17" s="2"/>
+      <c r="K17" s="2"/>
+      <c r="L17" s="2"/>
+      <c r="M17" s="2"/>
+      <c r="N17" s="2"/>
+      <c r="O17" s="2"/>
+      <c r="P17" s="2"/>
+      <c r="Q17" s="2"/>
+      <c r="R17" s="2"/>
+      <c r="S17" s="2"/>
+      <c r="T17" s="2"/>
+      <c r="U17" s="2"/>
+      <c r="V17" s="2"/>
+      <c r="W17" s="2"/>
+      <c r="X17" s="2"/>
+    </row>
+    <row r="18" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A18" s="2"/>
+      <c r="B18" s="2"/>
+      <c r="C18" s="2"/>
+      <c r="D18" s="2"/>
+      <c r="E18" s="2"/>
+      <c r="F18" s="2"/>
+      <c r="G18" s="2"/>
+      <c r="H18" s="2"/>
+      <c r="I18" s="2"/>
+      <c r="J18" s="2"/>
+      <c r="K18" s="2"/>
+      <c r="L18" s="2"/>
+      <c r="M18" s="2"/>
+      <c r="N18" s="2"/>
+      <c r="O18" s="2"/>
+      <c r="P18" s="2"/>
+      <c r="Q18" s="2"/>
+      <c r="R18" s="2"/>
+      <c r="S18" s="2"/>
+      <c r="T18" s="2"/>
+      <c r="U18" s="2"/>
+      <c r="V18" s="2"/>
+      <c r="W18" s="2"/>
+      <c r="X18" s="2"/>
+    </row>
+    <row r="19" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A19" s="2"/>
+      <c r="B19" s="2"/>
+      <c r="C19" s="2"/>
+      <c r="D19" s="2"/>
+      <c r="E19" s="2"/>
+      <c r="F19" s="2"/>
+      <c r="G19" s="2"/>
+      <c r="H19" s="2"/>
+      <c r="I19" s="2"/>
+      <c r="J19" s="2"/>
+      <c r="K19" s="2"/>
+      <c r="L19" s="2"/>
+      <c r="M19" s="2"/>
+      <c r="N19" s="2"/>
+      <c r="O19" s="2"/>
+      <c r="P19" s="2"/>
+      <c r="Q19" s="2"/>
+      <c r="R19" s="2"/>
+      <c r="S19" s="2"/>
+      <c r="T19" s="2"/>
+      <c r="U19" s="2"/>
+      <c r="V19" s="2"/>
+      <c r="W19" s="2"/>
+      <c r="X19" s="2"/>
+    </row>
+    <row r="20" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A20" s="2"/>
+      <c r="B20" s="2"/>
+      <c r="C20" s="2"/>
+      <c r="D20" s="2"/>
+      <c r="E20" s="2"/>
+      <c r="F20" s="2"/>
+      <c r="G20" s="2"/>
+      <c r="H20" s="2"/>
+      <c r="I20" s="2"/>
+      <c r="J20" s="2"/>
+      <c r="K20" s="2"/>
+      <c r="L20" s="2"/>
+      <c r="M20" s="2"/>
+      <c r="N20" s="2"/>
+      <c r="O20" s="2"/>
+      <c r="P20" s="2"/>
+      <c r="Q20" s="2"/>
+      <c r="R20" s="2"/>
+      <c r="S20" s="2"/>
+      <c r="T20" s="2"/>
+      <c r="U20" s="2"/>
+      <c r="V20" s="2"/>
+      <c r="W20" s="2"/>
+      <c r="X20" s="2"/>
+    </row>
+    <row r="21" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A21" s="2"/>
+      <c r="B21" s="2"/>
+      <c r="C21" s="2"/>
+      <c r="D21" s="2"/>
+      <c r="E21" s="2"/>
+      <c r="F21" s="2"/>
+      <c r="G21" s="2"/>
+      <c r="H21" s="2"/>
+      <c r="I21" s="2"/>
+      <c r="J21" s="2"/>
+      <c r="K21" s="2"/>
+      <c r="L21" s="2"/>
+      <c r="M21" s="2"/>
+      <c r="N21" s="2"/>
+      <c r="O21" s="2"/>
+      <c r="P21" s="2"/>
+      <c r="Q21" s="2"/>
+      <c r="R21" s="2"/>
+      <c r="S21" s="2"/>
+      <c r="T21" s="2"/>
+      <c r="U21" s="2"/>
+      <c r="V21" s="2"/>
+      <c r="W21" s="2"/>
+      <c r="X21" s="2"/>
+    </row>
+    <row r="22" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A22" s="2"/>
+      <c r="B22" s="2"/>
+      <c r="C22" s="2"/>
+      <c r="D22" s="2"/>
+      <c r="E22" s="2"/>
+      <c r="F22" s="2"/>
+      <c r="G22" s="2"/>
+      <c r="H22" s="2"/>
+      <c r="I22" s="2"/>
+      <c r="J22" s="2"/>
+      <c r="K22" s="2"/>
+      <c r="L22" s="2"/>
+      <c r="M22" s="2"/>
+      <c r="N22" s="2"/>
+      <c r="O22" s="2"/>
+      <c r="P22" s="2"/>
+      <c r="Q22" s="2"/>
+      <c r="R22" s="2"/>
+      <c r="S22" s="2"/>
+      <c r="T22" s="2"/>
+      <c r="U22" s="2"/>
+      <c r="V22" s="2"/>
+      <c r="W22" s="2"/>
+      <c r="X22" s="2"/>
+    </row>
+    <row r="23" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A23" s="2"/>
+      <c r="B23" s="2"/>
+      <c r="C23" s="2"/>
+      <c r="D23" s="2"/>
+      <c r="E23" s="2"/>
+      <c r="F23" s="2"/>
+      <c r="G23" s="2"/>
+      <c r="H23" s="2"/>
+      <c r="I23" s="2"/>
+      <c r="J23" s="2"/>
+      <c r="K23" s="2"/>
+      <c r="L23" s="2"/>
+      <c r="M23" s="2"/>
+      <c r="N23" s="2"/>
+      <c r="O23" s="2"/>
+      <c r="P23" s="2"/>
+      <c r="Q23" s="2"/>
+      <c r="R23" s="2"/>
+      <c r="S23" s="2"/>
+      <c r="T23" s="2"/>
+      <c r="U23" s="2"/>
+      <c r="V23" s="2"/>
+      <c r="W23" s="2"/>
+      <c r="X23" s="2"/>
+    </row>
+    <row r="24" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A24" s="2"/>
+      <c r="B24" s="2"/>
+      <c r="C24" s="2"/>
+      <c r="D24" s="2"/>
+      <c r="E24" s="2"/>
+      <c r="F24" s="2"/>
+      <c r="G24" s="2"/>
+      <c r="H24" s="2"/>
+      <c r="I24" s="2"/>
+      <c r="J24" s="2"/>
+      <c r="K24" s="2"/>
+      <c r="L24" s="2"/>
+      <c r="M24" s="2"/>
+      <c r="N24" s="2"/>
+      <c r="O24" s="2"/>
+      <c r="P24" s="2"/>
+      <c r="Q24" s="2"/>
+      <c r="R24" s="2"/>
+      <c r="S24" s="2"/>
+      <c r="T24" s="2"/>
+      <c r="U24" s="2"/>
+      <c r="V24" s="2"/>
+      <c r="W24" s="2"/>
+      <c r="X24" s="2"/>
+    </row>
+    <row r="25" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A25" s="2"/>
+      <c r="B25" s="2"/>
+      <c r="C25" s="2"/>
+      <c r="D25" s="2"/>
+      <c r="E25" s="2"/>
+      <c r="F25" s="2"/>
+      <c r="G25" s="2"/>
+      <c r="H25" s="2"/>
+      <c r="I25" s="2"/>
+      <c r="J25" s="2"/>
+      <c r="K25" s="2"/>
+      <c r="L25" s="2"/>
+      <c r="M25" s="2"/>
+      <c r="N25" s="2"/>
+      <c r="O25" s="2"/>
+      <c r="P25" s="2"/>
+      <c r="Q25" s="2"/>
+      <c r="R25" s="2"/>
+      <c r="S25" s="2"/>
+      <c r="T25" s="2"/>
+      <c r="U25" s="2"/>
+      <c r="V25" s="2"/>
+      <c r="W25" s="2"/>
+      <c r="X25" s="2"/>
+    </row>
+    <row r="26" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A26" s="2"/>
+      <c r="B26" s="2"/>
+      <c r="C26" s="2"/>
+      <c r="D26" s="2"/>
+      <c r="E26" s="2"/>
+      <c r="F26" s="2"/>
+      <c r="G26" s="2"/>
+      <c r="H26" s="2"/>
+      <c r="I26" s="2"/>
+      <c r="J26" s="2"/>
+      <c r="K26" s="2"/>
+      <c r="L26" s="2"/>
+      <c r="M26" s="2"/>
+      <c r="N26" s="2"/>
+      <c r="O26" s="2"/>
+      <c r="P26" s="2"/>
+      <c r="Q26" s="2"/>
+      <c r="R26" s="2"/>
+      <c r="S26" s="2"/>
+      <c r="T26" s="2"/>
+      <c r="U26" s="2"/>
+      <c r="V26" s="2"/>
+      <c r="W26" s="2"/>
+      <c r="X26" s="2"/>
+    </row>
+    <row r="27" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A27" s="2"/>
+      <c r="B27" s="2"/>
+      <c r="C27" s="2"/>
+      <c r="D27" s="2"/>
+      <c r="E27" s="2"/>
+      <c r="F27" s="2"/>
+      <c r="G27" s="2"/>
+      <c r="H27" s="2"/>
+      <c r="I27" s="2"/>
+      <c r="J27" s="2"/>
+      <c r="K27" s="2"/>
+      <c r="L27" s="2"/>
+      <c r="M27" s="2"/>
+      <c r="N27" s="2"/>
+      <c r="O27" s="2"/>
+      <c r="P27" s="2"/>
+      <c r="Q27" s="2"/>
+      <c r="R27" s="2"/>
+      <c r="S27" s="2"/>
+      <c r="T27" s="2"/>
+      <c r="U27" s="2"/>
+      <c r="V27" s="2"/>
+      <c r="W27" s="2"/>
+      <c r="X27" s="2"/>
+    </row>
+    <row r="28" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A28" s="2"/>
+      <c r="B28" s="2"/>
+      <c r="C28" s="2"/>
+      <c r="D28" s="2"/>
+      <c r="E28" s="2"/>
+      <c r="F28" s="2"/>
+      <c r="G28" s="2"/>
+      <c r="H28" s="2"/>
+      <c r="I28" s="2"/>
+      <c r="J28" s="2"/>
+      <c r="K28" s="2"/>
+      <c r="L28" s="2"/>
+      <c r="M28" s="2"/>
+      <c r="N28" s="2"/>
+      <c r="O28" s="2"/>
+      <c r="P28" s="2"/>
+      <c r="Q28" s="2"/>
+      <c r="R28" s="2"/>
+      <c r="S28" s="2"/>
+      <c r="T28" s="2"/>
+      <c r="U28" s="2"/>
+      <c r="V28" s="2"/>
+      <c r="W28" s="2"/>
+      <c r="X28" s="2"/>
+    </row>
+    <row r="29" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A29" s="2"/>
+      <c r="B29" s="2"/>
+      <c r="C29" s="2"/>
+      <c r="D29" s="2"/>
+      <c r="E29" s="2"/>
+      <c r="F29" s="2"/>
+      <c r="G29" s="2"/>
+      <c r="H29" s="2"/>
+      <c r="I29" s="2"/>
+      <c r="J29" s="2"/>
+      <c r="K29" s="2"/>
+      <c r="L29" s="2"/>
+      <c r="M29" s="2"/>
+      <c r="N29" s="2"/>
+      <c r="O29" s="2"/>
+      <c r="P29" s="2"/>
+      <c r="Q29" s="2"/>
+      <c r="R29" s="2"/>
+      <c r="S29" s="2"/>
+      <c r="T29" s="2"/>
+      <c r="U29" s="2"/>
+      <c r="V29" s="2"/>
+      <c r="W29" s="2"/>
+      <c r="X29" s="2"/>
+    </row>
+    <row r="30" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A30" s="2"/>
+      <c r="B30" s="2"/>
+      <c r="C30" s="2"/>
+      <c r="D30" s="2"/>
+      <c r="E30" s="2"/>
+      <c r="F30" s="2"/>
+      <c r="G30" s="2"/>
+      <c r="H30" s="2"/>
+      <c r="I30" s="2"/>
+      <c r="J30" s="2"/>
+      <c r="K30" s="2"/>
+      <c r="L30" s="2"/>
+      <c r="M30" s="2"/>
+      <c r="N30" s="2"/>
+      <c r="O30" s="2"/>
+      <c r="P30" s="2"/>
+      <c r="Q30" s="2"/>
+      <c r="R30" s="2"/>
+      <c r="S30" s="2"/>
+      <c r="T30" s="2"/>
+      <c r="U30" s="2"/>
+      <c r="V30" s="2"/>
+      <c r="W30" s="2"/>
+      <c r="X30" s="2"/>
+    </row>
+    <row r="31" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A31" s="2"/>
+      <c r="B31" s="2"/>
+      <c r="C31" s="2"/>
+      <c r="D31" s="2"/>
+      <c r="E31" s="2"/>
+      <c r="F31" s="2"/>
+      <c r="G31" s="2"/>
+      <c r="H31" s="2"/>
+      <c r="I31" s="2"/>
+      <c r="J31" s="2"/>
+      <c r="K31" s="2"/>
+      <c r="L31" s="2"/>
+      <c r="M31" s="2"/>
+      <c r="N31" s="2"/>
+      <c r="O31" s="2"/>
+      <c r="P31" s="2"/>
+      <c r="Q31" s="2"/>
+      <c r="R31" s="2"/>
+      <c r="S31" s="2"/>
+      <c r="T31" s="2"/>
+      <c r="U31" s="2"/>
+      <c r="V31" s="2"/>
+      <c r="W31" s="2"/>
+      <c r="X31" s="2"/>
+    </row>
+    <row r="32" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A32" s="2"/>
+      <c r="B32" s="2"/>
+      <c r="C32" s="2"/>
+      <c r="D32" s="2"/>
+      <c r="E32" s="2"/>
+      <c r="F32" s="2"/>
+      <c r="G32" s="2"/>
+      <c r="H32" s="2"/>
+      <c r="I32" s="2"/>
+      <c r="J32" s="2"/>
+      <c r="K32" s="2"/>
+      <c r="L32" s="2"/>
+      <c r="M32" s="2"/>
+      <c r="N32" s="2"/>
+      <c r="O32" s="2"/>
+      <c r="P32" s="2"/>
+      <c r="Q32" s="2"/>
+      <c r="R32" s="2"/>
+      <c r="S32" s="2"/>
+      <c r="T32" s="2"/>
+      <c r="U32" s="2"/>
+      <c r="V32" s="2"/>
+      <c r="W32" s="2"/>
+      <c r="X32" s="2"/>
+    </row>
+    <row r="33" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A33" s="2"/>
+      <c r="B33" s="2"/>
+      <c r="C33" s="2"/>
+      <c r="D33" s="2"/>
+      <c r="E33" s="2"/>
+      <c r="F33" s="2"/>
+      <c r="G33" s="2"/>
+      <c r="H33" s="2"/>
+      <c r="I33" s="2"/>
+      <c r="J33" s="2"/>
+      <c r="K33" s="2"/>
+      <c r="L33" s="2"/>
+      <c r="M33" s="2"/>
+      <c r="N33" s="2"/>
+      <c r="O33" s="2"/>
+      <c r="P33" s="2"/>
+      <c r="Q33" s="2"/>
+      <c r="R33" s="2"/>
+      <c r="S33" s="2"/>
+      <c r="T33" s="2"/>
+      <c r="U33" s="2"/>
+      <c r="V33" s="2"/>
+      <c r="W33" s="2"/>
+      <c r="X33" s="2"/>
+    </row>
+    <row r="34" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A34" s="2"/>
+      <c r="B34" s="2"/>
+      <c r="C34" s="2"/>
+      <c r="D34" s="2"/>
+      <c r="E34" s="2"/>
+      <c r="F34" s="2"/>
+      <c r="G34" s="2"/>
+      <c r="H34" s="2"/>
+      <c r="I34" s="2"/>
+      <c r="J34" s="2"/>
+      <c r="K34" s="2"/>
+      <c r="L34" s="2"/>
+      <c r="M34" s="2"/>
+      <c r="N34" s="2"/>
+      <c r="O34" s="2"/>
+      <c r="P34" s="2"/>
+      <c r="Q34" s="2"/>
+      <c r="R34" s="2"/>
+      <c r="S34" s="2"/>
+      <c r="T34" s="2"/>
+      <c r="U34" s="2"/>
+      <c r="V34" s="2"/>
+      <c r="W34" s="2"/>
+      <c r="X34" s="2"/>
+    </row>
+    <row r="35" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A35" s="2"/>
+      <c r="B35" s="2"/>
+      <c r="C35" s="2"/>
+      <c r="D35" s="2"/>
+      <c r="E35" s="2"/>
+      <c r="F35" s="2"/>
+      <c r="G35" s="2"/>
+      <c r="H35" s="2"/>
+      <c r="I35" s="2"/>
+      <c r="J35" s="2"/>
+      <c r="K35" s="2"/>
+      <c r="L35" s="2"/>
+      <c r="M35" s="2"/>
+      <c r="N35" s="2"/>
+      <c r="O35" s="2"/>
+      <c r="P35" s="2"/>
+      <c r="Q35" s="2"/>
+      <c r="R35" s="2"/>
+      <c r="S35" s="2"/>
+      <c r="T35" s="2"/>
+      <c r="U35" s="2"/>
+      <c r="V35" s="2"/>
+      <c r="W35" s="2"/>
+      <c r="X35" s="2"/>
+    </row>
+    <row r="36" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A36" s="2"/>
+      <c r="B36" s="2"/>
+      <c r="C36" s="2"/>
+      <c r="D36" s="2"/>
+      <c r="E36" s="2"/>
+      <c r="F36" s="2"/>
+      <c r="G36" s="2"/>
+      <c r="H36" s="2"/>
+      <c r="I36" s="2"/>
+      <c r="J36" s="2"/>
+      <c r="K36" s="2"/>
+      <c r="L36" s="2"/>
+      <c r="M36" s="2"/>
+      <c r="N36" s="2"/>
+      <c r="O36" s="2"/>
+      <c r="P36" s="2"/>
+      <c r="Q36" s="2"/>
+      <c r="R36" s="2"/>
+      <c r="S36" s="2"/>
+      <c r="T36" s="2"/>
+      <c r="U36" s="2"/>
+      <c r="V36" s="2"/>
+      <c r="W36" s="2"/>
+      <c r="X36" s="2"/>
+    </row>
+    <row r="37" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A37" s="2"/>
+      <c r="B37" s="2"/>
+      <c r="C37" s="2"/>
+      <c r="D37" s="2"/>
+      <c r="E37" s="2"/>
+      <c r="F37" s="2"/>
+      <c r="G37" s="2"/>
+      <c r="H37" s="2"/>
+      <c r="I37" s="2"/>
+      <c r="J37" s="2"/>
+      <c r="K37" s="2"/>
+      <c r="L37" s="2"/>
+      <c r="M37" s="2"/>
+      <c r="N37" s="2"/>
+      <c r="O37" s="2"/>
+      <c r="P37" s="2"/>
+      <c r="Q37" s="2"/>
+      <c r="R37" s="2"/>
+      <c r="S37" s="2"/>
+      <c r="T37" s="2"/>
+      <c r="U37" s="2"/>
+      <c r="V37" s="2"/>
+      <c r="W37" s="2"/>
+      <c r="X37" s="2"/>
+    </row>
+    <row r="38" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A38" s="2"/>
+      <c r="B38" s="2"/>
+      <c r="C38" s="2"/>
+      <c r="D38" s="2"/>
+      <c r="E38" s="2"/>
+      <c r="F38" s="2"/>
+      <c r="G38" s="2"/>
+      <c r="H38" s="2"/>
+      <c r="I38" s="2"/>
+      <c r="J38" s="2"/>
+      <c r="K38" s="2"/>
+      <c r="L38" s="2"/>
+      <c r="M38" s="2"/>
+      <c r="N38" s="2"/>
+      <c r="O38" s="2"/>
+      <c r="P38" s="2"/>
+      <c r="Q38" s="2"/>
+      <c r="R38" s="2"/>
+      <c r="S38" s="2"/>
+      <c r="T38" s="2"/>
+      <c r="U38" s="2"/>
+      <c r="V38" s="2"/>
+      <c r="W38" s="2"/>
+      <c r="X38" s="2"/>
+    </row>
+    <row r="39" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A39" s="2"/>
+      <c r="B39" s="2"/>
+      <c r="C39" s="2"/>
+      <c r="D39" s="2"/>
+      <c r="E39" s="2"/>
+      <c r="F39" s="2"/>
+      <c r="G39" s="2"/>
+      <c r="H39" s="2"/>
+      <c r="I39" s="2"/>
+      <c r="J39" s="2"/>
+      <c r="K39" s="2"/>
+      <c r="L39" s="2"/>
+      <c r="M39" s="2"/>
+      <c r="N39" s="2"/>
+      <c r="O39" s="2"/>
+      <c r="P39" s="2"/>
+      <c r="Q39" s="2"/>
+      <c r="R39" s="2"/>
+      <c r="S39" s="2"/>
+      <c r="T39" s="2"/>
+      <c r="U39" s="2"/>
+      <c r="V39" s="2"/>
+      <c r="W39" s="2"/>
+      <c r="X39" s="2"/>
+    </row>
+    <row r="40" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A40" s="2"/>
+      <c r="B40" s="2"/>
+      <c r="C40" s="2"/>
+      <c r="D40" s="2"/>
+      <c r="E40" s="2"/>
+      <c r="F40" s="2"/>
+      <c r="G40" s="2"/>
+      <c r="H40" s="2"/>
+      <c r="I40" s="2"/>
+      <c r="J40" s="2"/>
+      <c r="K40" s="2"/>
+      <c r="L40" s="2"/>
+      <c r="M40" s="2"/>
+      <c r="N40" s="2"/>
+      <c r="O40" s="2"/>
+      <c r="P40" s="2"/>
+      <c r="Q40" s="2"/>
+      <c r="R40" s="2"/>
+      <c r="S40" s="2"/>
+      <c r="T40" s="2"/>
+      <c r="U40" s="2"/>
+      <c r="V40" s="2"/>
+      <c r="W40" s="2"/>
+      <c r="X40" s="2"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -581,90 +2671,1107 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:B11"/>
+  <dimension ref="A1:X40"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
-    <col min="1" max="24" width="13.571428571428571" customWidth="1"/>
+    <col min="1" max="2" width="13.571428571428571" customWidth="1"/>
+    <col min="3" max="3" width="20" customWidth="1"/>
+    <col min="4" max="24" width="13.571428571428571" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A1" t="s">
+    <row r="1" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>4</v>
-      </c>
-      <c r="B2">
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1"/>
+      <c r="E1" s="1"/>
+      <c r="F1" s="1"/>
+      <c r="G1" s="1"/>
+      <c r="H1" s="1"/>
+      <c r="I1" s="1"/>
+      <c r="J1" s="1"/>
+      <c r="K1" s="1"/>
+      <c r="L1" s="1"/>
+      <c r="M1" s="1"/>
+      <c r="N1" s="1"/>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+      <c r="T1" s="1"/>
+      <c r="U1" s="1"/>
+      <c r="V1" s="1"/>
+      <c r="W1" s="1"/>
+      <c r="X1" s="1"/>
+    </row>
+    <row r="2" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A2" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B2" s="2">
         <v>4028609</v>
       </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>16</v>
-      </c>
-      <c r="B3" t="s">
+      <c r="C2" s="2">
+        <v>4028609</v>
+      </c>
+      <c r="D2" s="2"/>
+      <c r="E2" s="2"/>
+      <c r="F2" s="2"/>
+      <c r="G2" s="2"/>
+      <c r="H2" s="2"/>
+      <c r="I2" s="2"/>
+      <c r="J2" s="2"/>
+      <c r="K2" s="2"/>
+      <c r="L2" s="2"/>
+      <c r="M2" s="2"/>
+      <c r="N2" s="2"/>
+      <c r="O2" s="2"/>
+      <c r="P2" s="2"/>
+      <c r="Q2" s="2"/>
+      <c r="R2" s="2"/>
+      <c r="S2" s="2"/>
+      <c r="T2" s="2"/>
+      <c r="U2" s="2"/>
+      <c r="V2" s="2"/>
+      <c r="W2" s="2"/>
+      <c r="X2" s="2"/>
+    </row>
+    <row r="3" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A3" s="2" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
+      <c r="B3" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="B4">
+      <c r="C3" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="D3" s="2"/>
+      <c r="E3" s="2"/>
+      <c r="F3" s="2"/>
+      <c r="G3" s="2"/>
+      <c r="H3" s="2"/>
+      <c r="I3" s="2"/>
+      <c r="J3" s="2"/>
+      <c r="K3" s="2"/>
+      <c r="L3" s="2"/>
+      <c r="M3" s="2"/>
+      <c r="N3" s="2"/>
+      <c r="O3" s="2"/>
+      <c r="P3" s="2"/>
+      <c r="Q3" s="2"/>
+      <c r="R3" s="2"/>
+      <c r="S3" s="2"/>
+      <c r="T3" s="2"/>
+      <c r="U3" s="2"/>
+      <c r="V3" s="2"/>
+      <c r="W3" s="2"/>
+      <c r="X3" s="2"/>
+    </row>
+    <row r="4" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A4" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="B4" s="2">
         <v>4028609548494</v>
       </c>
-    </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
+      <c r="C4" s="2">
+        <v>4028609548494</v>
+      </c>
+      <c r="D4" s="2"/>
+      <c r="E4" s="2"/>
+      <c r="F4" s="2"/>
+      <c r="G4" s="2"/>
+      <c r="H4" s="2"/>
+      <c r="I4" s="2"/>
+      <c r="J4" s="2"/>
+      <c r="K4" s="2"/>
+      <c r="L4" s="2"/>
+      <c r="M4" s="2"/>
+      <c r="N4" s="2"/>
+      <c r="O4" s="2"/>
+      <c r="P4" s="2"/>
+      <c r="Q4" s="2"/>
+      <c r="R4" s="2"/>
+      <c r="S4" s="2"/>
+      <c r="T4" s="2"/>
+      <c r="U4" s="2"/>
+      <c r="V4" s="2"/>
+      <c r="W4" s="2"/>
+      <c r="X4" s="2"/>
+    </row>
+    <row r="5" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A5" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="B6">
+      <c r="B5" s="2"/>
+      <c r="C5" s="2"/>
+      <c r="D5" s="2"/>
+      <c r="E5" s="2"/>
+      <c r="F5" s="2"/>
+      <c r="G5" s="2"/>
+      <c r="H5" s="2"/>
+      <c r="I5" s="2"/>
+      <c r="J5" s="2"/>
+      <c r="K5" s="2"/>
+      <c r="L5" s="2"/>
+      <c r="M5" s="2"/>
+      <c r="N5" s="2"/>
+      <c r="O5" s="2"/>
+      <c r="P5" s="2"/>
+      <c r="Q5" s="2"/>
+      <c r="R5" s="2"/>
+      <c r="S5" s="2"/>
+      <c r="T5" s="2"/>
+      <c r="U5" s="2"/>
+      <c r="V5" s="2"/>
+      <c r="W5" s="2"/>
+      <c r="X5" s="2"/>
+    </row>
+    <row r="6" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A6" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="B6" s="2">
         <v>8555555</v>
       </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
-        <v>21</v>
-      </c>
-      <c r="B7" t="s">
+      <c r="C6" s="2">
+        <v>8555555</v>
+      </c>
+      <c r="D6" s="2"/>
+      <c r="E6" s="2"/>
+      <c r="F6" s="2"/>
+      <c r="G6" s="2"/>
+      <c r="H6" s="2"/>
+      <c r="I6" s="2"/>
+      <c r="J6" s="2"/>
+      <c r="K6" s="2"/>
+      <c r="L6" s="2"/>
+      <c r="M6" s="2"/>
+      <c r="N6" s="2"/>
+      <c r="O6" s="2"/>
+      <c r="P6" s="2"/>
+      <c r="Q6" s="2"/>
+      <c r="R6" s="2"/>
+      <c r="S6" s="2"/>
+      <c r="T6" s="2"/>
+      <c r="U6" s="2"/>
+      <c r="V6" s="2"/>
+      <c r="W6" s="2"/>
+      <c r="X6" s="2"/>
+    </row>
+    <row r="7" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A7" s="2" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="8" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
+      <c r="B7" s="2" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="9" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
+      <c r="C7" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="D7" s="2"/>
+      <c r="E7" s="2"/>
+      <c r="F7" s="2"/>
+      <c r="G7" s="2"/>
+      <c r="H7" s="2"/>
+      <c r="I7" s="2"/>
+      <c r="J7" s="2"/>
+      <c r="K7" s="2"/>
+      <c r="L7" s="2"/>
+      <c r="M7" s="2"/>
+      <c r="N7" s="2"/>
+      <c r="O7" s="2"/>
+      <c r="P7" s="2"/>
+      <c r="Q7" s="2"/>
+      <c r="R7" s="2"/>
+      <c r="S7" s="2"/>
+      <c r="T7" s="2"/>
+      <c r="U7" s="2"/>
+      <c r="V7" s="2"/>
+      <c r="W7" s="2"/>
+      <c r="X7" s="2"/>
+    </row>
+    <row r="8" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A8" s="2" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
+      <c r="B8" s="2"/>
+      <c r="C8" s="2"/>
+      <c r="D8" s="2"/>
+      <c r="E8" s="2"/>
+      <c r="F8" s="2"/>
+      <c r="G8" s="2"/>
+      <c r="H8" s="2"/>
+      <c r="I8" s="2"/>
+      <c r="J8" s="2"/>
+      <c r="K8" s="2"/>
+      <c r="L8" s="2"/>
+      <c r="M8" s="2"/>
+      <c r="N8" s="2"/>
+      <c r="O8" s="2"/>
+      <c r="P8" s="2"/>
+      <c r="Q8" s="2"/>
+      <c r="R8" s="2"/>
+      <c r="S8" s="2"/>
+      <c r="T8" s="2"/>
+      <c r="U8" s="2"/>
+      <c r="V8" s="2"/>
+      <c r="W8" s="2"/>
+      <c r="X8" s="2"/>
+    </row>
+    <row r="9" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A9" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="B10" t="s">
+      <c r="B9" s="2"/>
+      <c r="C9" s="2"/>
+      <c r="D9" s="2"/>
+      <c r="E9" s="2"/>
+      <c r="F9" s="2"/>
+      <c r="G9" s="2"/>
+      <c r="H9" s="2"/>
+      <c r="I9" s="2"/>
+      <c r="J9" s="2"/>
+      <c r="K9" s="2"/>
+      <c r="L9" s="2"/>
+      <c r="M9" s="2"/>
+      <c r="N9" s="2"/>
+      <c r="O9" s="2"/>
+      <c r="P9" s="2"/>
+      <c r="Q9" s="2"/>
+      <c r="R9" s="2"/>
+      <c r="S9" s="2"/>
+      <c r="T9" s="2"/>
+      <c r="U9" s="2"/>
+      <c r="V9" s="2"/>
+      <c r="W9" s="2"/>
+      <c r="X9" s="2"/>
+    </row>
+    <row r="10" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A10" s="2" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
-        <v>5</v>
-      </c>
-      <c r="B11" t="s">
+      <c r="B10" s="2" t="s">
         <v>27</v>
       </c>
+      <c r="C10" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="D10" s="2"/>
+      <c r="E10" s="2"/>
+      <c r="F10" s="2"/>
+      <c r="G10" s="2"/>
+      <c r="H10" s="2"/>
+      <c r="I10" s="2"/>
+      <c r="J10" s="2"/>
+      <c r="K10" s="2"/>
+      <c r="L10" s="2"/>
+      <c r="M10" s="2"/>
+      <c r="N10" s="2"/>
+      <c r="O10" s="2"/>
+      <c r="P10" s="2"/>
+      <c r="Q10" s="2"/>
+      <c r="R10" s="2"/>
+      <c r="S10" s="2"/>
+      <c r="T10" s="2"/>
+      <c r="U10" s="2"/>
+      <c r="V10" s="2"/>
+      <c r="W10" s="2"/>
+      <c r="X10" s="2"/>
+    </row>
+    <row r="11" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A11" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="D11" s="2"/>
+      <c r="E11" s="2"/>
+      <c r="F11" s="2"/>
+      <c r="G11" s="2"/>
+      <c r="H11" s="2"/>
+      <c r="I11" s="2"/>
+      <c r="J11" s="2"/>
+      <c r="K11" s="2"/>
+      <c r="L11" s="2"/>
+      <c r="M11" s="2"/>
+      <c r="N11" s="2"/>
+      <c r="O11" s="2"/>
+      <c r="P11" s="2"/>
+      <c r="Q11" s="2"/>
+      <c r="R11" s="2"/>
+      <c r="S11" s="2"/>
+      <c r="T11" s="2"/>
+      <c r="U11" s="2"/>
+      <c r="V11" s="2"/>
+      <c r="W11" s="2"/>
+      <c r="X11" s="2"/>
+    </row>
+    <row r="12" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A12" s="2"/>
+      <c r="B12" s="2"/>
+      <c r="C12" s="2"/>
+      <c r="D12" s="2"/>
+      <c r="E12" s="2"/>
+      <c r="F12" s="2"/>
+      <c r="G12" s="2"/>
+      <c r="H12" s="2"/>
+      <c r="I12" s="2"/>
+      <c r="J12" s="2"/>
+      <c r="K12" s="2"/>
+      <c r="L12" s="2"/>
+      <c r="M12" s="2"/>
+      <c r="N12" s="2"/>
+      <c r="O12" s="2"/>
+      <c r="P12" s="2"/>
+      <c r="Q12" s="2"/>
+      <c r="R12" s="2"/>
+      <c r="S12" s="2"/>
+      <c r="T12" s="2"/>
+      <c r="U12" s="2"/>
+      <c r="V12" s="2"/>
+      <c r="W12" s="2"/>
+      <c r="X12" s="2"/>
+    </row>
+    <row r="13" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A13" s="2"/>
+      <c r="B13" s="2"/>
+      <c r="C13" s="2"/>
+      <c r="D13" s="2"/>
+      <c r="E13" s="2"/>
+      <c r="F13" s="2"/>
+      <c r="G13" s="2"/>
+      <c r="H13" s="2"/>
+      <c r="I13" s="2"/>
+      <c r="J13" s="2"/>
+      <c r="K13" s="2"/>
+      <c r="L13" s="2"/>
+      <c r="M13" s="2"/>
+      <c r="N13" s="2"/>
+      <c r="O13" s="2"/>
+      <c r="P13" s="2"/>
+      <c r="Q13" s="2"/>
+      <c r="R13" s="2"/>
+      <c r="S13" s="2"/>
+      <c r="T13" s="2"/>
+      <c r="U13" s="2"/>
+      <c r="V13" s="2"/>
+      <c r="W13" s="2"/>
+      <c r="X13" s="2"/>
+    </row>
+    <row r="14" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A14" s="2"/>
+      <c r="B14" s="2"/>
+      <c r="C14" s="2"/>
+      <c r="D14" s="2"/>
+      <c r="E14" s="2"/>
+      <c r="F14" s="2"/>
+      <c r="G14" s="2"/>
+      <c r="H14" s="2"/>
+      <c r="I14" s="2"/>
+      <c r="J14" s="2"/>
+      <c r="K14" s="2"/>
+      <c r="L14" s="2"/>
+      <c r="M14" s="2"/>
+      <c r="N14" s="2"/>
+      <c r="O14" s="2"/>
+      <c r="P14" s="2"/>
+      <c r="Q14" s="2"/>
+      <c r="R14" s="2"/>
+      <c r="S14" s="2"/>
+      <c r="T14" s="2"/>
+      <c r="U14" s="2"/>
+      <c r="V14" s="2"/>
+      <c r="W14" s="2"/>
+      <c r="X14" s="2"/>
+    </row>
+    <row r="15" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A15" s="2"/>
+      <c r="B15" s="2"/>
+      <c r="C15" s="2"/>
+      <c r="D15" s="2"/>
+      <c r="E15" s="2"/>
+      <c r="F15" s="2"/>
+      <c r="G15" s="2"/>
+      <c r="H15" s="2"/>
+      <c r="I15" s="2"/>
+      <c r="J15" s="2"/>
+      <c r="K15" s="2"/>
+      <c r="L15" s="2"/>
+      <c r="M15" s="2"/>
+      <c r="N15" s="2"/>
+      <c r="O15" s="2"/>
+      <c r="P15" s="2"/>
+      <c r="Q15" s="2"/>
+      <c r="R15" s="2"/>
+      <c r="S15" s="2"/>
+      <c r="T15" s="2"/>
+      <c r="U15" s="2"/>
+      <c r="V15" s="2"/>
+      <c r="W15" s="2"/>
+      <c r="X15" s="2"/>
+    </row>
+    <row r="16" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A16" s="2"/>
+      <c r="B16" s="2"/>
+      <c r="C16" s="2"/>
+      <c r="D16" s="2"/>
+      <c r="E16" s="2"/>
+      <c r="F16" s="2"/>
+      <c r="G16" s="2"/>
+      <c r="H16" s="2"/>
+      <c r="I16" s="2"/>
+      <c r="J16" s="2"/>
+      <c r="K16" s="2"/>
+      <c r="L16" s="2"/>
+      <c r="M16" s="2"/>
+      <c r="N16" s="2"/>
+      <c r="O16" s="2"/>
+      <c r="P16" s="2"/>
+      <c r="Q16" s="2"/>
+      <c r="R16" s="2"/>
+      <c r="S16" s="2"/>
+      <c r="T16" s="2"/>
+      <c r="U16" s="2"/>
+      <c r="V16" s="2"/>
+      <c r="W16" s="2"/>
+      <c r="X16" s="2"/>
+    </row>
+    <row r="17" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A17" s="2"/>
+      <c r="B17" s="2"/>
+      <c r="C17" s="2"/>
+      <c r="D17" s="2"/>
+      <c r="E17" s="2"/>
+      <c r="F17" s="2"/>
+      <c r="G17" s="2"/>
+      <c r="H17" s="2"/>
+      <c r="I17" s="2"/>
+      <c r="J17" s="2"/>
+      <c r="K17" s="2"/>
+      <c r="L17" s="2"/>
+      <c r="M17" s="2"/>
+      <c r="N17" s="2"/>
+      <c r="O17" s="2"/>
+      <c r="P17" s="2"/>
+      <c r="Q17" s="2"/>
+      <c r="R17" s="2"/>
+      <c r="S17" s="2"/>
+      <c r="T17" s="2"/>
+      <c r="U17" s="2"/>
+      <c r="V17" s="2"/>
+      <c r="W17" s="2"/>
+      <c r="X17" s="2"/>
+    </row>
+    <row r="18" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A18" s="2"/>
+      <c r="B18" s="2"/>
+      <c r="C18" s="2"/>
+      <c r="D18" s="2"/>
+      <c r="E18" s="2"/>
+      <c r="F18" s="2"/>
+      <c r="G18" s="2"/>
+      <c r="H18" s="2"/>
+      <c r="I18" s="2"/>
+      <c r="J18" s="2"/>
+      <c r="K18" s="2"/>
+      <c r="L18" s="2"/>
+      <c r="M18" s="2"/>
+      <c r="N18" s="2"/>
+      <c r="O18" s="2"/>
+      <c r="P18" s="2"/>
+      <c r="Q18" s="2"/>
+      <c r="R18" s="2"/>
+      <c r="S18" s="2"/>
+      <c r="T18" s="2"/>
+      <c r="U18" s="2"/>
+      <c r="V18" s="2"/>
+      <c r="W18" s="2"/>
+      <c r="X18" s="2"/>
+    </row>
+    <row r="19" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A19" s="2"/>
+      <c r="B19" s="2"/>
+      <c r="C19" s="2"/>
+      <c r="D19" s="2"/>
+      <c r="E19" s="2"/>
+      <c r="F19" s="2"/>
+      <c r="G19" s="2"/>
+      <c r="H19" s="2"/>
+      <c r="I19" s="2"/>
+      <c r="J19" s="2"/>
+      <c r="K19" s="2"/>
+      <c r="L19" s="2"/>
+      <c r="M19" s="2"/>
+      <c r="N19" s="2"/>
+      <c r="O19" s="2"/>
+      <c r="P19" s="2"/>
+      <c r="Q19" s="2"/>
+      <c r="R19" s="2"/>
+      <c r="S19" s="2"/>
+      <c r="T19" s="2"/>
+      <c r="U19" s="2"/>
+      <c r="V19" s="2"/>
+      <c r="W19" s="2"/>
+      <c r="X19" s="2"/>
+    </row>
+    <row r="20" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A20" s="2"/>
+      <c r="B20" s="2"/>
+      <c r="C20" s="2"/>
+      <c r="D20" s="2"/>
+      <c r="E20" s="2"/>
+      <c r="F20" s="2"/>
+      <c r="G20" s="2"/>
+      <c r="H20" s="2"/>
+      <c r="I20" s="2"/>
+      <c r="J20" s="2"/>
+      <c r="K20" s="2"/>
+      <c r="L20" s="2"/>
+      <c r="M20" s="2"/>
+      <c r="N20" s="2"/>
+      <c r="O20" s="2"/>
+      <c r="P20" s="2"/>
+      <c r="Q20" s="2"/>
+      <c r="R20" s="2"/>
+      <c r="S20" s="2"/>
+      <c r="T20" s="2"/>
+      <c r="U20" s="2"/>
+      <c r="V20" s="2"/>
+      <c r="W20" s="2"/>
+      <c r="X20" s="2"/>
+    </row>
+    <row r="21" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A21" s="2"/>
+      <c r="B21" s="2"/>
+      <c r="C21" s="2"/>
+      <c r="D21" s="2"/>
+      <c r="E21" s="2"/>
+      <c r="F21" s="2"/>
+      <c r="G21" s="2"/>
+      <c r="H21" s="2"/>
+      <c r="I21" s="2"/>
+      <c r="J21" s="2"/>
+      <c r="K21" s="2"/>
+      <c r="L21" s="2"/>
+      <c r="M21" s="2"/>
+      <c r="N21" s="2"/>
+      <c r="O21" s="2"/>
+      <c r="P21" s="2"/>
+      <c r="Q21" s="2"/>
+      <c r="R21" s="2"/>
+      <c r="S21" s="2"/>
+      <c r="T21" s="2"/>
+      <c r="U21" s="2"/>
+      <c r="V21" s="2"/>
+      <c r="W21" s="2"/>
+      <c r="X21" s="2"/>
+    </row>
+    <row r="22" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A22" s="2"/>
+      <c r="B22" s="2"/>
+      <c r="C22" s="2"/>
+      <c r="D22" s="2"/>
+      <c r="E22" s="2"/>
+      <c r="F22" s="2"/>
+      <c r="G22" s="2"/>
+      <c r="H22" s="2"/>
+      <c r="I22" s="2"/>
+      <c r="J22" s="2"/>
+      <c r="K22" s="2"/>
+      <c r="L22" s="2"/>
+      <c r="M22" s="2"/>
+      <c r="N22" s="2"/>
+      <c r="O22" s="2"/>
+      <c r="P22" s="2"/>
+      <c r="Q22" s="2"/>
+      <c r="R22" s="2"/>
+      <c r="S22" s="2"/>
+      <c r="T22" s="2"/>
+      <c r="U22" s="2"/>
+      <c r="V22" s="2"/>
+      <c r="W22" s="2"/>
+      <c r="X22" s="2"/>
+    </row>
+    <row r="23" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A23" s="2"/>
+      <c r="B23" s="2"/>
+      <c r="C23" s="2"/>
+      <c r="D23" s="2"/>
+      <c r="E23" s="2"/>
+      <c r="F23" s="2"/>
+      <c r="G23" s="2"/>
+      <c r="H23" s="2"/>
+      <c r="I23" s="2"/>
+      <c r="J23" s="2"/>
+      <c r="K23" s="2"/>
+      <c r="L23" s="2"/>
+      <c r="M23" s="2"/>
+      <c r="N23" s="2"/>
+      <c r="O23" s="2"/>
+      <c r="P23" s="2"/>
+      <c r="Q23" s="2"/>
+      <c r="R23" s="2"/>
+      <c r="S23" s="2"/>
+      <c r="T23" s="2"/>
+      <c r="U23" s="2"/>
+      <c r="V23" s="2"/>
+      <c r="W23" s="2"/>
+      <c r="X23" s="2"/>
+    </row>
+    <row r="24" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A24" s="2"/>
+      <c r="B24" s="2"/>
+      <c r="C24" s="2"/>
+      <c r="D24" s="2"/>
+      <c r="E24" s="2"/>
+      <c r="F24" s="2"/>
+      <c r="G24" s="2"/>
+      <c r="H24" s="2"/>
+      <c r="I24" s="2"/>
+      <c r="J24" s="2"/>
+      <c r="K24" s="2"/>
+      <c r="L24" s="2"/>
+      <c r="M24" s="2"/>
+      <c r="N24" s="2"/>
+      <c r="O24" s="2"/>
+      <c r="P24" s="2"/>
+      <c r="Q24" s="2"/>
+      <c r="R24" s="2"/>
+      <c r="S24" s="2"/>
+      <c r="T24" s="2"/>
+      <c r="U24" s="2"/>
+      <c r="V24" s="2"/>
+      <c r="W24" s="2"/>
+      <c r="X24" s="2"/>
+    </row>
+    <row r="25" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A25" s="2"/>
+      <c r="B25" s="2"/>
+      <c r="C25" s="2"/>
+      <c r="D25" s="2"/>
+      <c r="E25" s="2"/>
+      <c r="F25" s="2"/>
+      <c r="G25" s="2"/>
+      <c r="H25" s="2"/>
+      <c r="I25" s="2"/>
+      <c r="J25" s="2"/>
+      <c r="K25" s="2"/>
+      <c r="L25" s="2"/>
+      <c r="M25" s="2"/>
+      <c r="N25" s="2"/>
+      <c r="O25" s="2"/>
+      <c r="P25" s="2"/>
+      <c r="Q25" s="2"/>
+      <c r="R25" s="2"/>
+      <c r="S25" s="2"/>
+      <c r="T25" s="2"/>
+      <c r="U25" s="2"/>
+      <c r="V25" s="2"/>
+      <c r="W25" s="2"/>
+      <c r="X25" s="2"/>
+    </row>
+    <row r="26" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A26" s="2"/>
+      <c r="B26" s="2"/>
+      <c r="C26" s="2"/>
+      <c r="D26" s="2"/>
+      <c r="E26" s="2"/>
+      <c r="F26" s="2"/>
+      <c r="G26" s="2"/>
+      <c r="H26" s="2"/>
+      <c r="I26" s="2"/>
+      <c r="J26" s="2"/>
+      <c r="K26" s="2"/>
+      <c r="L26" s="2"/>
+      <c r="M26" s="2"/>
+      <c r="N26" s="2"/>
+      <c r="O26" s="2"/>
+      <c r="P26" s="2"/>
+      <c r="Q26" s="2"/>
+      <c r="R26" s="2"/>
+      <c r="S26" s="2"/>
+      <c r="T26" s="2"/>
+      <c r="U26" s="2"/>
+      <c r="V26" s="2"/>
+      <c r="W26" s="2"/>
+      <c r="X26" s="2"/>
+    </row>
+    <row r="27" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A27" s="2"/>
+      <c r="B27" s="2"/>
+      <c r="C27" s="2"/>
+      <c r="D27" s="2"/>
+      <c r="E27" s="2"/>
+      <c r="F27" s="2"/>
+      <c r="G27" s="2"/>
+      <c r="H27" s="2"/>
+      <c r="I27" s="2"/>
+      <c r="J27" s="2"/>
+      <c r="K27" s="2"/>
+      <c r="L27" s="2"/>
+      <c r="M27" s="2"/>
+      <c r="N27" s="2"/>
+      <c r="O27" s="2"/>
+      <c r="P27" s="2"/>
+      <c r="Q27" s="2"/>
+      <c r="R27" s="2"/>
+      <c r="S27" s="2"/>
+      <c r="T27" s="2"/>
+      <c r="U27" s="2"/>
+      <c r="V27" s="2"/>
+      <c r="W27" s="2"/>
+      <c r="X27" s="2"/>
+    </row>
+    <row r="28" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A28" s="2"/>
+      <c r="B28" s="2"/>
+      <c r="C28" s="2"/>
+      <c r="D28" s="2"/>
+      <c r="E28" s="2"/>
+      <c r="F28" s="2"/>
+      <c r="G28" s="2"/>
+      <c r="H28" s="2"/>
+      <c r="I28" s="2"/>
+      <c r="J28" s="2"/>
+      <c r="K28" s="2"/>
+      <c r="L28" s="2"/>
+      <c r="M28" s="2"/>
+      <c r="N28" s="2"/>
+      <c r="O28" s="2"/>
+      <c r="P28" s="2"/>
+      <c r="Q28" s="2"/>
+      <c r="R28" s="2"/>
+      <c r="S28" s="2"/>
+      <c r="T28" s="2"/>
+      <c r="U28" s="2"/>
+      <c r="V28" s="2"/>
+      <c r="W28" s="2"/>
+      <c r="X28" s="2"/>
+    </row>
+    <row r="29" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A29" s="2"/>
+      <c r="B29" s="2"/>
+      <c r="C29" s="2"/>
+      <c r="D29" s="2"/>
+      <c r="E29" s="2"/>
+      <c r="F29" s="2"/>
+      <c r="G29" s="2"/>
+      <c r="H29" s="2"/>
+      <c r="I29" s="2"/>
+      <c r="J29" s="2"/>
+      <c r="K29" s="2"/>
+      <c r="L29" s="2"/>
+      <c r="M29" s="2"/>
+      <c r="N29" s="2"/>
+      <c r="O29" s="2"/>
+      <c r="P29" s="2"/>
+      <c r="Q29" s="2"/>
+      <c r="R29" s="2"/>
+      <c r="S29" s="2"/>
+      <c r="T29" s="2"/>
+      <c r="U29" s="2"/>
+      <c r="V29" s="2"/>
+      <c r="W29" s="2"/>
+      <c r="X29" s="2"/>
+    </row>
+    <row r="30" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A30" s="2"/>
+      <c r="B30" s="2"/>
+      <c r="C30" s="2"/>
+      <c r="D30" s="2"/>
+      <c r="E30" s="2"/>
+      <c r="F30" s="2"/>
+      <c r="G30" s="2"/>
+      <c r="H30" s="2"/>
+      <c r="I30" s="2"/>
+      <c r="J30" s="2"/>
+      <c r="K30" s="2"/>
+      <c r="L30" s="2"/>
+      <c r="M30" s="2"/>
+      <c r="N30" s="2"/>
+      <c r="O30" s="2"/>
+      <c r="P30" s="2"/>
+      <c r="Q30" s="2"/>
+      <c r="R30" s="2"/>
+      <c r="S30" s="2"/>
+      <c r="T30" s="2"/>
+      <c r="U30" s="2"/>
+      <c r="V30" s="2"/>
+      <c r="W30" s="2"/>
+      <c r="X30" s="2"/>
+    </row>
+    <row r="31" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A31" s="2"/>
+      <c r="B31" s="2"/>
+      <c r="C31" s="2"/>
+      <c r="D31" s="2"/>
+      <c r="E31" s="2"/>
+      <c r="F31" s="2"/>
+      <c r="G31" s="2"/>
+      <c r="H31" s="2"/>
+      <c r="I31" s="2"/>
+      <c r="J31" s="2"/>
+      <c r="K31" s="2"/>
+      <c r="L31" s="2"/>
+      <c r="M31" s="2"/>
+      <c r="N31" s="2"/>
+      <c r="O31" s="2"/>
+      <c r="P31" s="2"/>
+      <c r="Q31" s="2"/>
+      <c r="R31" s="2"/>
+      <c r="S31" s="2"/>
+      <c r="T31" s="2"/>
+      <c r="U31" s="2"/>
+      <c r="V31" s="2"/>
+      <c r="W31" s="2"/>
+      <c r="X31" s="2"/>
+    </row>
+    <row r="32" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A32" s="2"/>
+      <c r="B32" s="2"/>
+      <c r="C32" s="2"/>
+      <c r="D32" s="2"/>
+      <c r="E32" s="2"/>
+      <c r="F32" s="2"/>
+      <c r="G32" s="2"/>
+      <c r="H32" s="2"/>
+      <c r="I32" s="2"/>
+      <c r="J32" s="2"/>
+      <c r="K32" s="2"/>
+      <c r="L32" s="2"/>
+      <c r="M32" s="2"/>
+      <c r="N32" s="2"/>
+      <c r="O32" s="2"/>
+      <c r="P32" s="2"/>
+      <c r="Q32" s="2"/>
+      <c r="R32" s="2"/>
+      <c r="S32" s="2"/>
+      <c r="T32" s="2"/>
+      <c r="U32" s="2"/>
+      <c r="V32" s="2"/>
+      <c r="W32" s="2"/>
+      <c r="X32" s="2"/>
+    </row>
+    <row r="33" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A33" s="2"/>
+      <c r="B33" s="2"/>
+      <c r="C33" s="2"/>
+      <c r="D33" s="2"/>
+      <c r="E33" s="2"/>
+      <c r="F33" s="2"/>
+      <c r="G33" s="2"/>
+      <c r="H33" s="2"/>
+      <c r="I33" s="2"/>
+      <c r="J33" s="2"/>
+      <c r="K33" s="2"/>
+      <c r="L33" s="2"/>
+      <c r="M33" s="2"/>
+      <c r="N33" s="2"/>
+      <c r="O33" s="2"/>
+      <c r="P33" s="2"/>
+      <c r="Q33" s="2"/>
+      <c r="R33" s="2"/>
+      <c r="S33" s="2"/>
+      <c r="T33" s="2"/>
+      <c r="U33" s="2"/>
+      <c r="V33" s="2"/>
+      <c r="W33" s="2"/>
+      <c r="X33" s="2"/>
+    </row>
+    <row r="34" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A34" s="2"/>
+      <c r="B34" s="2"/>
+      <c r="C34" s="2"/>
+      <c r="D34" s="2"/>
+      <c r="E34" s="2"/>
+      <c r="F34" s="2"/>
+      <c r="G34" s="2"/>
+      <c r="H34" s="2"/>
+      <c r="I34" s="2"/>
+      <c r="J34" s="2"/>
+      <c r="K34" s="2"/>
+      <c r="L34" s="2"/>
+      <c r="M34" s="2"/>
+      <c r="N34" s="2"/>
+      <c r="O34" s="2"/>
+      <c r="P34" s="2"/>
+      <c r="Q34" s="2"/>
+      <c r="R34" s="2"/>
+      <c r="S34" s="2"/>
+      <c r="T34" s="2"/>
+      <c r="U34" s="2"/>
+      <c r="V34" s="2"/>
+      <c r="W34" s="2"/>
+      <c r="X34" s="2"/>
+    </row>
+    <row r="35" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A35" s="2"/>
+      <c r="B35" s="2"/>
+      <c r="C35" s="2"/>
+      <c r="D35" s="2"/>
+      <c r="E35" s="2"/>
+      <c r="F35" s="2"/>
+      <c r="G35" s="2"/>
+      <c r="H35" s="2"/>
+      <c r="I35" s="2"/>
+      <c r="J35" s="2"/>
+      <c r="K35" s="2"/>
+      <c r="L35" s="2"/>
+      <c r="M35" s="2"/>
+      <c r="N35" s="2"/>
+      <c r="O35" s="2"/>
+      <c r="P35" s="2"/>
+      <c r="Q35" s="2"/>
+      <c r="R35" s="2"/>
+      <c r="S35" s="2"/>
+      <c r="T35" s="2"/>
+      <c r="U35" s="2"/>
+      <c r="V35" s="2"/>
+      <c r="W35" s="2"/>
+      <c r="X35" s="2"/>
+    </row>
+    <row r="36" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A36" s="2"/>
+      <c r="B36" s="2"/>
+      <c r="C36" s="2"/>
+      <c r="D36" s="2"/>
+      <c r="E36" s="2"/>
+      <c r="F36" s="2"/>
+      <c r="G36" s="2"/>
+      <c r="H36" s="2"/>
+      <c r="I36" s="2"/>
+      <c r="J36" s="2"/>
+      <c r="K36" s="2"/>
+      <c r="L36" s="2"/>
+      <c r="M36" s="2"/>
+      <c r="N36" s="2"/>
+      <c r="O36" s="2"/>
+      <c r="P36" s="2"/>
+      <c r="Q36" s="2"/>
+      <c r="R36" s="2"/>
+      <c r="S36" s="2"/>
+      <c r="T36" s="2"/>
+      <c r="U36" s="2"/>
+      <c r="V36" s="2"/>
+      <c r="W36" s="2"/>
+      <c r="X36" s="2"/>
+    </row>
+    <row r="37" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A37" s="2"/>
+      <c r="B37" s="2"/>
+      <c r="C37" s="2"/>
+      <c r="D37" s="2"/>
+      <c r="E37" s="2"/>
+      <c r="F37" s="2"/>
+      <c r="G37" s="2"/>
+      <c r="H37" s="2"/>
+      <c r="I37" s="2"/>
+      <c r="J37" s="2"/>
+      <c r="K37" s="2"/>
+      <c r="L37" s="2"/>
+      <c r="M37" s="2"/>
+      <c r="N37" s="2"/>
+      <c r="O37" s="2"/>
+      <c r="P37" s="2"/>
+      <c r="Q37" s="2"/>
+      <c r="R37" s="2"/>
+      <c r="S37" s="2"/>
+      <c r="T37" s="2"/>
+      <c r="U37" s="2"/>
+      <c r="V37" s="2"/>
+      <c r="W37" s="2"/>
+      <c r="X37" s="2"/>
+    </row>
+    <row r="38" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A38" s="2"/>
+      <c r="B38" s="2"/>
+      <c r="C38" s="2"/>
+      <c r="D38" s="2"/>
+      <c r="E38" s="2"/>
+      <c r="F38" s="2"/>
+      <c r="G38" s="2"/>
+      <c r="H38" s="2"/>
+      <c r="I38" s="2"/>
+      <c r="J38" s="2"/>
+      <c r="K38" s="2"/>
+      <c r="L38" s="2"/>
+      <c r="M38" s="2"/>
+      <c r="N38" s="2"/>
+      <c r="O38" s="2"/>
+      <c r="P38" s="2"/>
+      <c r="Q38" s="2"/>
+      <c r="R38" s="2"/>
+      <c r="S38" s="2"/>
+      <c r="T38" s="2"/>
+      <c r="U38" s="2"/>
+      <c r="V38" s="2"/>
+      <c r="W38" s="2"/>
+      <c r="X38" s="2"/>
+    </row>
+    <row r="39" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A39" s="2"/>
+      <c r="B39" s="2"/>
+      <c r="C39" s="2"/>
+      <c r="D39" s="2"/>
+      <c r="E39" s="2"/>
+      <c r="F39" s="2"/>
+      <c r="G39" s="2"/>
+      <c r="H39" s="2"/>
+      <c r="I39" s="2"/>
+      <c r="J39" s="2"/>
+      <c r="K39" s="2"/>
+      <c r="L39" s="2"/>
+      <c r="M39" s="2"/>
+      <c r="N39" s="2"/>
+      <c r="O39" s="2"/>
+      <c r="P39" s="2"/>
+      <c r="Q39" s="2"/>
+      <c r="R39" s="2"/>
+      <c r="S39" s="2"/>
+      <c r="T39" s="2"/>
+      <c r="U39" s="2"/>
+      <c r="V39" s="2"/>
+      <c r="W39" s="2"/>
+      <c r="X39" s="2"/>
+    </row>
+    <row r="40" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A40" s="2"/>
+      <c r="B40" s="2"/>
+      <c r="C40" s="2"/>
+      <c r="D40" s="2"/>
+      <c r="E40" s="2"/>
+      <c r="F40" s="2"/>
+      <c r="G40" s="2"/>
+      <c r="H40" s="2"/>
+      <c r="I40" s="2"/>
+      <c r="J40" s="2"/>
+      <c r="K40" s="2"/>
+      <c r="L40" s="2"/>
+      <c r="M40" s="2"/>
+      <c r="N40" s="2"/>
+      <c r="O40" s="2"/>
+      <c r="P40" s="2"/>
+      <c r="Q40" s="2"/>
+      <c r="R40" s="2"/>
+      <c r="S40" s="2"/>
+      <c r="T40" s="2"/>
+      <c r="U40" s="2"/>
+      <c r="V40" s="2"/>
+      <c r="W40" s="2"/>
+      <c r="X40" s="2"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/data/excel/TestData.xlsx
+++ b/data/excel/TestData.xlsx
@@ -1,49 +1,139 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <workbookPr codeName="ThisWorkbook" defaultThemeVersion="164011" filterPrivacy="true"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
+  <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
   <sheets>
-    <sheet name="Login" sheetId="1" r:id="rId1"/>
-    <sheet name="Dashboard" sheetId="2" r:id="rId2"/>
-    <sheet name="ForgotPassword" sheetId="3" r:id="rId3"/>
+    <sheet sheetId="1" name="Login" state="visible" r:id="rId4"/>
+    <sheet sheetId="2" name="Dashboard" state="visible" r:id="rId5"/>
+    <sheet sheetId="3" name="ForgotPassword" state="visible" r:id="rId6"/>
   </sheets>
+  <calcPr calcId="171027"/>
 </workbook>
 </file>
 
-<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
-  <metadataTypes count="1">
-    <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
-  </metadataTypes>
-  <futureMetadata name="XLDAPR" count="1">
-    <bk>
-      <extLst>
-        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
-          <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
-        </ext>
-      </extLst>
-    </bk>
-  </futureMetadata>
-  <cellMetadata count="1">
-    <bk>
-      <rc t="1" v="0"/>
-    </bk>
-  </cellMetadata>
-</metadata>
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="99" uniqueCount="36">
+  <si>
+    <t>Key</t>
+  </si>
+  <si>
+    <t>staging</t>
+  </si>
+  <si>
+    <t>production</t>
+  </si>
+  <si>
+    <t>title</t>
+  </si>
+  <si>
+    <t>EMIS | Tamil Nadu Schools</t>
+  </si>
+  <si>
+    <t>validUser</t>
+  </si>
+  <si>
+    <t>validPassword</t>
+  </si>
+  <si>
+    <t>test@123</t>
+  </si>
+  <si>
+    <t>Pete@9119</t>
+  </si>
+  <si>
+    <t>invalidUser</t>
+  </si>
+  <si>
+    <t>jkdbfbjdsbvi</t>
+  </si>
+  <si>
+    <t>invalidPassword</t>
+  </si>
+  <si>
+    <t>dhhdsuivb</t>
+  </si>
+  <si>
+    <t>space</t>
+  </si>
+  <si>
+    <t xml:space="preserve">   </t>
+  </si>
+  <si>
+    <t>SNo</t>
+  </si>
+  <si>
+    <t>Name</t>
+  </si>
+  <si>
+    <t>BEO</t>
+  </si>
+  <si>
+    <t>username</t>
+  </si>
+  <si>
+    <t>password</t>
+  </si>
+  <si>
+    <t>9688@1986</t>
+  </si>
+  <si>
+    <t>BEO1</t>
+  </si>
+  <si>
+    <t>9488@1967</t>
+  </si>
+  <si>
+    <t>BRC_Senior_Officer</t>
+  </si>
+  <si>
+    <t>invalidUser1</t>
+  </si>
+  <si>
+    <t>40286@..09</t>
+  </si>
+  <si>
+    <t>invalidUser2</t>
+  </si>
+  <si>
+    <t>spaceUser</t>
+  </si>
+  <si>
+    <t>invalidOtp1</t>
+  </si>
+  <si>
+    <t>invalidOtp2</t>
+  </si>
+  <si>
+    <t>@@@@.....</t>
+  </si>
+  <si>
+    <t>validOtp</t>
+  </si>
+  <si>
+    <t>invalidPassword1</t>
+  </si>
+  <si>
+    <t>invalidPassword2</t>
+  </si>
+  <si>
+    <t>test123</t>
+  </si>
+  <si>
+    <t>Test@1234</t>
+  </si>
+</sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:vt="http://schemas.openxmlformats.org/officeDocument/2006/docPropsVTypes">
-  <numFmts count="1">
-    <numFmt numFmtId="56" formatCode="&quot;上午/下午 &quot;hh&quot;時&quot;mm&quot;分&quot;ss&quot;秒 &quot;"/>
-  </numFmts>
-  <fonts count="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+  <fonts count="1" x14ac:knownFonts="1">
     <font>
-      <sz val="12"/>
       <color theme="1"/>
-      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+      <sz val="11"/>
+      <name val="Calibri"/>
     </font>
   </fonts>
   <fills count="2">
@@ -67,13 +157,21 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleMedium4"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -398,34 +496,38 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:X40"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:C7"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <cols>
+    <col min="1" max="24" width="13.571428571428571" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="str">
-        <v>Key</v>
-      </c>
-      <c r="B1" t="str">
-        <v>staging</v>
-      </c>
-      <c r="C1" t="str">
-        <v>production</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="str">
-        <v>title</v>
-      </c>
-      <c r="B2" t="str">
-        <v>EMIS | Tamil Nadu Schools</v>
-      </c>
-      <c r="C2" t="str">
-        <v>EMIS | Tamil Nadu Schools</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="str">
-        <v>validUser</v>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B2" t="s">
+        <v>4</v>
+      </c>
+      <c r="C2" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>5</v>
       </c>
       <c r="B3">
         <v>4028609</v>
@@ -434,185 +536,415 @@
         <v>4028619</v>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" t="str">
-        <v>validPassword</v>
-      </c>
-      <c r="B4" t="str">
-        <v>test@123</v>
-      </c>
-      <c r="C4" t="str">
-        <v>Pete@9119</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="str">
-        <v>invalidUser</v>
-      </c>
-      <c r="B5" t="str">
-        <v>jkdbfbjdsbvi</v>
-      </c>
-      <c r="C5" t="str">
-        <v>jkdbfbjdsbvi</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="str">
-        <v>invalidPassword</v>
-      </c>
-      <c r="B6" t="str">
-        <v>dhhdsuivb</v>
-      </c>
-      <c r="C6" t="str">
-        <v>dhhdsuivb</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="str">
-        <v>space</v>
-      </c>
-      <c r="B7" t="str">
-        <v xml:space="preserve">   </v>
-      </c>
-      <c r="C7" t="str">
-        <v xml:space="preserve">   </v>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>6</v>
+      </c>
+      <c r="B4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C4" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C5" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>11</v>
+      </c>
+      <c r="B6" t="s">
+        <v>12</v>
+      </c>
+      <c r="C6" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>13</v>
+      </c>
+      <c r="B7" t="s">
+        <v>14</v>
+      </c>
+      <c r="C7" t="s">
+        <v>14</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:X40"/>
-  </ignoredErrors>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D7"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:E19"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <cols>
+    <col min="1" max="24" width="13.571428571428571" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="str">
-        <v>Name</v>
-      </c>
-      <c r="B1" t="str">
-        <v>Key</v>
-      </c>
-      <c r="C1" t="str">
-        <v>staging</v>
-      </c>
-      <c r="D1" t="str">
-        <v>production</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="str">
-        <v>BEO</v>
-      </c>
-      <c r="B2" t="str">
-        <v>username</v>
-      </c>
-      <c r="C2" t="str">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C1" t="s">
+        <v>0</v>
+      </c>
+      <c r="D1" t="s">
+        <v>1</v>
+      </c>
+      <c r="E1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A2">
+        <v>1</v>
+      </c>
+      <c r="B2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C2" t="s">
+        <v>18</v>
+      </c>
+      <c r="D2">
+        <v>30648666</v>
+      </c>
+      <c r="E2">
+        <v>30648666</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A3">
+        <v>1</v>
+      </c>
+      <c r="B3" t="s">
+        <v>17</v>
+      </c>
+      <c r="C3" t="s">
+        <v>19</v>
+      </c>
+      <c r="D3" t="s">
+        <v>20</v>
+      </c>
+      <c r="E3" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4">
+        <v>2</v>
+      </c>
+      <c r="B4" t="s">
+        <v>17</v>
+      </c>
+      <c r="C4" t="s">
+        <v>18</v>
+      </c>
+      <c r="D4">
+        <v>4028619</v>
+      </c>
+      <c r="E4">
+        <v>4028619</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A5">
+        <v>2</v>
+      </c>
+      <c r="B5" t="s">
+        <v>17</v>
+      </c>
+      <c r="C5" t="s">
+        <v>19</v>
+      </c>
+      <c r="D5" t="s">
+        <v>7</v>
+      </c>
+      <c r="E5" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A6">
+        <v>3</v>
+      </c>
+      <c r="B6" t="s">
+        <v>17</v>
+      </c>
+      <c r="C6" t="s">
+        <v>18</v>
+      </c>
+      <c r="D6">
+        <v>4028611</v>
+      </c>
+      <c r="E6">
+        <v>4028621</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A7">
+        <v>3</v>
+      </c>
+      <c r="B7" t="s">
+        <v>17</v>
+      </c>
+      <c r="C7" t="s">
+        <v>19</v>
+      </c>
+      <c r="D7" t="s">
+        <v>7</v>
+      </c>
+      <c r="E7" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A8">
+        <v>1</v>
+      </c>
+      <c r="B8" t="s">
+        <v>21</v>
+      </c>
+      <c r="C8" t="s">
+        <v>18</v>
+      </c>
+      <c r="D8">
+        <v>20233863</v>
+      </c>
+      <c r="E8">
+        <v>20233863</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A9">
+        <v>1</v>
+      </c>
+      <c r="B9" t="s">
+        <v>21</v>
+      </c>
+      <c r="C9" t="s">
+        <v>19</v>
+      </c>
+      <c r="D9" t="s">
+        <v>22</v>
+      </c>
+      <c r="E9" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A10">
+        <v>2</v>
+      </c>
+      <c r="B10" t="s">
+        <v>21</v>
+      </c>
+      <c r="C10" t="s">
+        <v>18</v>
+      </c>
+      <c r="D10">
+        <v>4028612</v>
+      </c>
+      <c r="E10">
+        <v>4028622</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A11">
+        <v>2</v>
+      </c>
+      <c r="B11" t="s">
+        <v>21</v>
+      </c>
+      <c r="C11" t="s">
+        <v>19</v>
+      </c>
+      <c r="D11" t="s">
+        <v>7</v>
+      </c>
+      <c r="E11" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A12">
+        <v>3</v>
+      </c>
+      <c r="B12" t="s">
+        <v>21</v>
+      </c>
+      <c r="C12" t="s">
+        <v>18</v>
+      </c>
+      <c r="D12">
+        <v>4028613</v>
+      </c>
+      <c r="E12">
+        <v>4028623</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A13">
+        <v>3</v>
+      </c>
+      <c r="B13" t="s">
+        <v>21</v>
+      </c>
+      <c r="C13" t="s">
+        <v>19</v>
+      </c>
+      <c r="D13" t="s">
+        <v>7</v>
+      </c>
+      <c r="E13" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A14">
+        <v>1</v>
+      </c>
+      <c r="B14" t="s">
+        <v>23</v>
+      </c>
+      <c r="C14" t="s">
+        <v>18</v>
+      </c>
+      <c r="D14">
         <v>4028609</v>
       </c>
-      <c r="D2" t="str">
+      <c r="E14">
         <v>4028619</v>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" t="str">
-        <v>BEO</v>
-      </c>
-      <c r="B3" t="str">
-        <v>password</v>
-      </c>
-      <c r="C3" t="str">
-        <v>test@123</v>
-      </c>
-      <c r="D3" t="str">
-        <v>Pete@9119</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="str">
-        <v>BEO1</v>
-      </c>
-      <c r="B4" t="str">
-        <v>username</v>
-      </c>
-      <c r="C4" t="str">
-        <v>4028609</v>
-      </c>
-      <c r="D4" t="str">
-        <v>4028619</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="str">
-        <v>BEO1</v>
-      </c>
-      <c r="B5" t="str">
-        <v>password</v>
-      </c>
-      <c r="C5" t="str">
-        <v>test@123</v>
-      </c>
-      <c r="D5" t="str">
-        <v>Pete@9119</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="str">
-        <v>BRC_Senior_Officer</v>
-      </c>
-      <c r="B6" t="str">
-        <v>username</v>
-      </c>
-      <c r="C6" t="str">
-        <v>4028609</v>
-      </c>
-      <c r="D6" t="str">
-        <v>4028619</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="str">
-        <v>BRC_Senior_Officer</v>
-      </c>
-      <c r="B7" t="str">
-        <v>password</v>
-      </c>
-      <c r="C7" t="str">
-        <v>test@123</v>
-      </c>
-      <c r="D7" t="str">
-        <v>Pete@9119</v>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A15">
+        <v>1</v>
+      </c>
+      <c r="B15" t="s">
+        <v>23</v>
+      </c>
+      <c r="C15" t="s">
+        <v>19</v>
+      </c>
+      <c r="D15" t="s">
+        <v>7</v>
+      </c>
+      <c r="E15" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A16">
+        <v>2</v>
+      </c>
+      <c r="B16" t="s">
+        <v>23</v>
+      </c>
+      <c r="C16" t="s">
+        <v>18</v>
+      </c>
+      <c r="D16">
+        <v>4028614</v>
+      </c>
+      <c r="E16">
+        <v>4028624</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A17">
+        <v>2</v>
+      </c>
+      <c r="B17" t="s">
+        <v>23</v>
+      </c>
+      <c r="C17" t="s">
+        <v>19</v>
+      </c>
+      <c r="D17" t="s">
+        <v>7</v>
+      </c>
+      <c r="E17" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A18">
+        <v>3</v>
+      </c>
+      <c r="B18" t="s">
+        <v>23</v>
+      </c>
+      <c r="C18" t="s">
+        <v>18</v>
+      </c>
+      <c r="D18">
+        <v>4028615</v>
+      </c>
+      <c r="E18">
+        <v>4028625</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A19">
+        <v>3</v>
+      </c>
+      <c r="B19" t="s">
+        <v>23</v>
+      </c>
+      <c r="C19" t="s">
+        <v>19</v>
+      </c>
+      <c r="D19" t="s">
+        <v>7</v>
+      </c>
+      <c r="E19" t="s">
+        <v>8</v>
       </c>
     </row>
   </sheetData>
-  <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:D7"/>
-  </ignoredErrors>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:X40"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:C11"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <cols>
+    <col min="1" max="24" width="13.571428571428571" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="str">
-        <v>Key</v>
-      </c>
-      <c r="B1" t="str">
-        <v>staging</v>
-      </c>
-      <c r="C1" t="str">
-        <v>production</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="str">
-        <v>validUser</v>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>5</v>
       </c>
       <c r="B2">
         <v>4028609</v>
@@ -621,20 +953,20 @@
         <v>4028609</v>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" t="str">
-        <v>invalidUser1</v>
-      </c>
-      <c r="B3" t="str">
-        <v>40286@..09</v>
-      </c>
-      <c r="C3" t="str">
-        <v>40286@..09</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="str">
-        <v>invalidUser2</v>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>24</v>
+      </c>
+      <c r="B3" t="s">
+        <v>25</v>
+      </c>
+      <c r="C3" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>26</v>
       </c>
       <c r="B4">
         <v>4028609548494</v>
@@ -643,14 +975,14 @@
         <v>4028609548494</v>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" t="str">
-        <v>spaceUser</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="str">
-        <v>invalidOtp1</v>
+    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>28</v>
       </c>
       <c r="B6">
         <v>8555555</v>
@@ -659,53 +991,51 @@
         <v>8555555</v>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" t="str">
-        <v>invalidOtp2</v>
-      </c>
-      <c r="B7" t="str">
-        <v>@@@@.....</v>
-      </c>
-      <c r="C7" t="str">
-        <v>@@@@.....</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="str">
-        <v>validOtp</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="str">
-        <v>invalidPassword1</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="str">
-        <v>invalidPassword2</v>
-      </c>
-      <c r="B10" t="str">
-        <v>test123</v>
-      </c>
-      <c r="C10" t="str">
-        <v>test123</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="str">
-        <v>validPassword</v>
-      </c>
-      <c r="B11" t="str">
-        <v>Test@1234</v>
-      </c>
-      <c r="C11" t="str">
-        <v>Test@1234</v>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>29</v>
+      </c>
+      <c r="B7" t="s">
+        <v>30</v>
+      </c>
+      <c r="C7" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="8" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="9" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>33</v>
+      </c>
+      <c r="B10" t="s">
+        <v>34</v>
+      </c>
+      <c r="C10" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>6</v>
+      </c>
+      <c r="B11" t="s">
+        <v>35</v>
+      </c>
+      <c r="C11" t="s">
+        <v>35</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:X40"/>
-  </ignoredErrors>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>
 </file>
--- a/data/excel/TestData.xlsx
+++ b/data/excel/TestData.xlsx
@@ -127,7 +127,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <color theme="1"/>
       <family val="2"/>
@@ -135,16 +135,31 @@
       <sz val="11"/>
       <name val="Calibri"/>
     </font>
+    <font>
+      <b/>
+      <sz val="14"/>
+      <name val="Times New Roman"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF8EAADA"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE3EFD9"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -152,12 +167,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -500,83 +524,86 @@
   <dimension ref="A1:C7"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
-    <col min="1" max="24" width="13.571428571428571" customWidth="1"/>
+    <col min="1" max="1" width="13.571428571428571" customWidth="1"/>
+    <col min="2" max="2" width="18.142857142857142" customWidth="1"/>
+    <col min="3" max="3" width="20.714285714285715" customWidth="1"/>
+    <col min="4" max="24" width="13.571428571428571" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A1" t="s">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
+      <c r="A2" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="C2" t="s">
+      <c r="C2" s="2" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
+      <c r="A3" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="B3">
+      <c r="B3" s="2">
         <v>4028609</v>
       </c>
-      <c r="C3">
+      <c r="C3" s="2">
         <v>4028619</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
+      <c r="A4" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="B4" t="s">
+      <c r="B4" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="C4" t="s">
+      <c r="C4" s="2" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
+      <c r="A5" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="B5" t="s">
+      <c r="B5" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="C5" t="s">
+      <c r="C5" s="2" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
+      <c r="A6" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="B6" t="s">
+      <c r="B6" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="C6" t="s">
+      <c r="C6" s="2" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
+      <c r="A7" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="B7" t="s">
+      <c r="B7" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="C7" t="s">
+      <c r="C7" s="2" t="s">
         <v>14</v>
       </c>
     </row>
@@ -591,329 +618,330 @@
   <dimension ref="A1:E19"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
-    <col min="1" max="24" width="13.571428571428571" customWidth="1"/>
+    <col min="1" max="5" width="14.714285714285714" customWidth="1"/>
+    <col min="6" max="24" width="13.571428571428571" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A1" t="s">
+      <c r="A1" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="E1" t="s">
+      <c r="E1" s="1" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A2">
+      <c r="A2" s="2">
         <v>1</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="C2" t="s">
+      <c r="C2" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="D2">
+      <c r="D2" s="2">
         <v>30648666</v>
       </c>
-      <c r="E2">
+      <c r="E2" s="2">
         <v>30648666</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A3">
+      <c r="A3" s="2">
         <v>1</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B3" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="C3" t="s">
+      <c r="C3" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="D3" t="s">
+      <c r="D3" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="E3" t="s">
+      <c r="E3" s="2" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A4">
+      <c r="A4" s="2">
         <v>2</v>
       </c>
-      <c r="B4" t="s">
+      <c r="B4" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="C4" t="s">
+      <c r="C4" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="D4">
+      <c r="D4" s="2">
         <v>4028619</v>
       </c>
-      <c r="E4">
+      <c r="E4" s="2">
         <v>4028619</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A5">
+      <c r="A5" s="2">
         <v>2</v>
       </c>
-      <c r="B5" t="s">
+      <c r="B5" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="C5" t="s">
+      <c r="C5" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="D5" t="s">
+      <c r="D5" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="E5" t="s">
+      <c r="E5" s="2" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A6">
+      <c r="A6" s="2">
         <v>3</v>
       </c>
-      <c r="B6" t="s">
+      <c r="B6" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="C6" t="s">
+      <c r="C6" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="D6">
+      <c r="D6" s="2">
         <v>4028611</v>
       </c>
-      <c r="E6">
+      <c r="E6" s="2">
         <v>4028621</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A7">
+      <c r="A7" s="2">
         <v>3</v>
       </c>
-      <c r="B7" t="s">
+      <c r="B7" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="C7" t="s">
+      <c r="C7" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="D7" t="s">
+      <c r="D7" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="E7" t="s">
+      <c r="E7" s="2" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A8">
+      <c r="A8" s="2">
         <v>1</v>
       </c>
-      <c r="B8" t="s">
+      <c r="B8" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="C8" t="s">
+      <c r="C8" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="D8">
+      <c r="D8" s="2">
         <v>20233863</v>
       </c>
-      <c r="E8">
+      <c r="E8" s="2">
         <v>20233863</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A9">
+      <c r="A9" s="2">
         <v>1</v>
       </c>
-      <c r="B9" t="s">
+      <c r="B9" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="C9" t="s">
+      <c r="C9" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="D9" t="s">
+      <c r="D9" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="E9" t="s">
+      <c r="E9" s="2" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A10">
+      <c r="A10" s="2">
         <v>2</v>
       </c>
-      <c r="B10" t="s">
+      <c r="B10" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="C10" t="s">
+      <c r="C10" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="D10">
+      <c r="D10" s="2">
         <v>4028612</v>
       </c>
-      <c r="E10">
+      <c r="E10" s="2">
         <v>4028622</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A11">
+      <c r="A11" s="2">
         <v>2</v>
       </c>
-      <c r="B11" t="s">
+      <c r="B11" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="C11" t="s">
+      <c r="C11" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="D11" t="s">
+      <c r="D11" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="E11" t="s">
+      <c r="E11" s="2" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A12">
+      <c r="A12" s="2">
         <v>3</v>
       </c>
-      <c r="B12" t="s">
+      <c r="B12" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="C12" t="s">
+      <c r="C12" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="D12">
+      <c r="D12" s="2">
         <v>4028613</v>
       </c>
-      <c r="E12">
+      <c r="E12" s="2">
         <v>4028623</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A13">
+      <c r="A13" s="2">
         <v>3</v>
       </c>
-      <c r="B13" t="s">
+      <c r="B13" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="C13" t="s">
+      <c r="C13" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="D13" t="s">
+      <c r="D13" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="E13" t="s">
+      <c r="E13" s="2" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A14">
+      <c r="A14" s="2">
         <v>1</v>
       </c>
-      <c r="B14" t="s">
+      <c r="B14" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="C14" t="s">
+      <c r="C14" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="D14">
+      <c r="D14" s="2">
         <v>4028609</v>
       </c>
-      <c r="E14">
+      <c r="E14" s="2">
         <v>4028619</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A15">
+      <c r="A15" s="2">
         <v>1</v>
       </c>
-      <c r="B15" t="s">
+      <c r="B15" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="C15" t="s">
+      <c r="C15" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="D15" t="s">
+      <c r="D15" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="E15" t="s">
+      <c r="E15" s="2" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A16">
+      <c r="A16" s="2">
         <v>2</v>
       </c>
-      <c r="B16" t="s">
+      <c r="B16" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="C16" t="s">
+      <c r="C16" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="D16">
+      <c r="D16" s="2">
         <v>4028614</v>
       </c>
-      <c r="E16">
+      <c r="E16" s="2">
         <v>4028624</v>
       </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A17">
+      <c r="A17" s="2">
         <v>2</v>
       </c>
-      <c r="B17" t="s">
+      <c r="B17" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="C17" t="s">
+      <c r="C17" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="D17" t="s">
+      <c r="D17" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="E17" t="s">
+      <c r="E17" s="2" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A18">
+      <c r="A18" s="2">
         <v>3</v>
       </c>
-      <c r="B18" t="s">
+      <c r="B18" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="C18" t="s">
+      <c r="C18" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="D18">
+      <c r="D18" s="2">
         <v>4028615</v>
       </c>
-      <c r="E18">
+      <c r="E18" s="2">
         <v>4028625</v>
       </c>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A19">
+      <c r="A19" s="2">
         <v>3</v>
       </c>
-      <c r="B19" t="s">
+      <c r="B19" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="C19" t="s">
+      <c r="C19" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="D19" t="s">
+      <c r="D19" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="E19" t="s">
+      <c r="E19" s="2" t="s">
         <v>8</v>
       </c>
     </row>
@@ -928,109 +956,116 @@
   <dimension ref="A1:C11"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
-    <col min="1" max="24" width="13.571428571428571" customWidth="1"/>
+    <col min="1" max="3" width="16.285714285714285" customWidth="1"/>
+    <col min="4" max="24" width="13.571428571428571" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A1" t="s">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
+      <c r="A2" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="B2">
+      <c r="B2" s="2">
         <v>4028609</v>
       </c>
-      <c r="C2">
+      <c r="C2" s="2">
         <v>4028609</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
+      <c r="A3" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B3" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="C3" t="s">
+      <c r="C3" s="2" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
+      <c r="A4" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="B4">
+      <c r="B4" s="2">
         <v>4028609548494</v>
       </c>
-      <c r="C4">
+      <c r="C4" s="2">
         <v>4028609548494</v>
       </c>
     </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5" s="2" t="s">
         <v>27</v>
       </c>
+      <c r="B5" s="2"/>
+      <c r="C5" s="2"/>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
+      <c r="A6" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="B6">
+      <c r="B6" s="2">
         <v>8555555</v>
       </c>
-      <c r="C6">
+      <c r="C6" s="2">
         <v>8555555</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
+      <c r="A7" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="B7" t="s">
+      <c r="B7" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="C7" t="s">
+      <c r="C7" s="2" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="8" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A8" s="2" t="s">
         <v>31</v>
       </c>
-    </row>
-    <row r="9" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
+      <c r="B8" s="2"/>
+      <c r="C8" s="2"/>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A9" s="2" t="s">
         <v>32</v>
       </c>
+      <c r="B9" s="2"/>
+      <c r="C9" s="2"/>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
+      <c r="A10" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="B10" t="s">
+      <c r="B10" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="C10" t="s">
+      <c r="C10" s="2" t="s">
         <v>34</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
+      <c r="A11" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="B11" t="s">
+      <c r="B11" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="C11" t="s">
+      <c r="C11" s="2" t="s">
         <v>35</v>
       </c>
     </row>
